--- a/research/traditional_assets/database/data/nigeria/nigeria_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_environmental_waste_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1611472551282691</v>
+        <v>0.1606953133628842</v>
       </c>
       <c r="C2">
-        <v>1.817878623845849</v>
+        <v>1.805433047390371</v>
       </c>
       <c r="D2">
-        <v>1.753878623845849</v>
+        <v>1.759333047390371</v>
       </c>
       <c r="E2">
-        <v>-0.35</v>
+        <v>-0.3321</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0179</v>
       </c>
       <c r="G2">
         <v>0.064</v>
@@ -1451,28 +1451,28 @@
         <v>0.584</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0009003699999999999</v>
       </c>
       <c r="N2">
-        <v>0.584</v>
+        <v>0.58309963</v>
       </c>
       <c r="O2">
-        <v>0.1752</v>
+        <v>0.174929889</v>
       </c>
       <c r="P2">
-        <v>0.4087999999999999</v>
+        <v>0.408169741</v>
       </c>
       <c r="Q2">
-        <v>0.4147999999999999</v>
+        <v>0.414169741</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1611472551282691</v>
+        <v>0.1619628417806911</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8099387413235496</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>648.6222330819552</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1606953133628842</v>
+        <v>0.1602433715974994</v>
       </c>
       <c r="C3">
-        <v>1.805433047390371</v>
+        <v>1.793021502420157</v>
       </c>
       <c r="D3">
-        <v>1.759333047390371</v>
+        <v>1.764821502420157</v>
       </c>
       <c r="E3">
-        <v>-0.3321</v>
+        <v>-0.3142</v>
       </c>
       <c r="F3">
-        <v>0.0179</v>
+        <v>0.0358</v>
       </c>
       <c r="G3">
         <v>0.064</v>
@@ -1533,28 +1533,28 @@
         <v>0.584</v>
       </c>
       <c r="M3">
-        <v>0.0009003699999999999</v>
+        <v>0.00180074</v>
       </c>
       <c r="N3">
-        <v>0.58309963</v>
+        <v>0.58219926</v>
       </c>
       <c r="O3">
-        <v>0.174929889</v>
+        <v>0.174659778</v>
       </c>
       <c r="P3">
-        <v>0.408169741</v>
+        <v>0.407539482</v>
       </c>
       <c r="Q3">
-        <v>0.414169741</v>
+        <v>0.413539482</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1619628417806911</v>
+        <v>0.1627950730586729</v>
       </c>
       <c r="T3">
-        <v>0.8099387413235496</v>
+        <v>0.8157414261016235</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>648.6222330819552</v>
+        <v>324.3111165409776</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1602433715974994</v>
+        <v>0.1597914298321146</v>
       </c>
       <c r="C4">
-        <v>1.793021502420157</v>
+        <v>1.780644308428067</v>
       </c>
       <c r="D4">
-        <v>1.764821502420157</v>
+        <v>1.770344308428067</v>
       </c>
       <c r="E4">
-        <v>-0.3142</v>
+        <v>-0.2963</v>
       </c>
       <c r="F4">
-        <v>0.0358</v>
+        <v>0.0537</v>
       </c>
       <c r="G4">
         <v>0.064</v>
@@ -1615,28 +1615,28 @@
         <v>0.584</v>
       </c>
       <c r="M4">
-        <v>0.00180074</v>
+        <v>0.00270111</v>
       </c>
       <c r="N4">
-        <v>0.58219926</v>
+        <v>0.58129889</v>
       </c>
       <c r="O4">
-        <v>0.174659778</v>
+        <v>0.174389667</v>
       </c>
       <c r="P4">
-        <v>0.407539482</v>
+        <v>0.406909223</v>
       </c>
       <c r="Q4">
-        <v>0.413539482</v>
+        <v>0.412909223</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1627950730586729</v>
+        <v>0.1636444637444481</v>
       </c>
       <c r="T4">
-        <v>0.8157414261016235</v>
+        <v>0.8216637538648123</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>324.3111165409776</v>
+        <v>216.2074110273184</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1597914298321146</v>
+        <v>0.1593394880667298</v>
       </c>
       <c r="C5">
-        <v>1.780644308428067</v>
+        <v>1.768301788918786</v>
       </c>
       <c r="D5">
-        <v>1.770344308428067</v>
+        <v>1.775901788918786</v>
       </c>
       <c r="E5">
-        <v>-0.2963</v>
+        <v>-0.2784</v>
       </c>
       <c r="F5">
-        <v>0.0537</v>
+        <v>0.0716</v>
       </c>
       <c r="G5">
         <v>0.064</v>
@@ -1697,28 +1697,28 @@
         <v>0.584</v>
       </c>
       <c r="M5">
-        <v>0.00270111</v>
+        <v>0.00360148</v>
       </c>
       <c r="N5">
-        <v>0.58129889</v>
+        <v>0.5803985199999999</v>
       </c>
       <c r="O5">
-        <v>0.174389667</v>
+        <v>0.174119556</v>
       </c>
       <c r="P5">
-        <v>0.406909223</v>
+        <v>0.406278964</v>
       </c>
       <c r="Q5">
-        <v>0.412909223</v>
+        <v>0.412278964</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1636444637444481</v>
+        <v>0.1645115500695102</v>
       </c>
       <c r="T5">
-        <v>0.8216637538648123</v>
+        <v>0.8277094634564007</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>216.2074110273184</v>
+        <v>162.1555582704888</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1593394880667298</v>
+        <v>0.158887546301345</v>
       </c>
       <c r="C6">
-        <v>1.768301788918786</v>
+        <v>1.755994271471982</v>
       </c>
       <c r="D6">
-        <v>1.775901788918786</v>
+        <v>1.781494271471982</v>
       </c>
       <c r="E6">
-        <v>-0.2784</v>
+        <v>-0.2605</v>
       </c>
       <c r="F6">
-        <v>0.0716</v>
+        <v>0.08950000000000001</v>
       </c>
       <c r="G6">
         <v>0.064</v>
@@ -1779,28 +1779,28 @@
         <v>0.584</v>
       </c>
       <c r="M6">
-        <v>0.00360148</v>
+        <v>0.00450185</v>
       </c>
       <c r="N6">
-        <v>0.5803985199999999</v>
+        <v>0.5794981499999999</v>
       </c>
       <c r="O6">
-        <v>0.174119556</v>
+        <v>0.173849445</v>
       </c>
       <c r="P6">
-        <v>0.406278964</v>
+        <v>0.4056487049999999</v>
       </c>
       <c r="Q6">
-        <v>0.412278964</v>
+        <v>0.4116487049999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1645115500695102</v>
+        <v>0.165396890843521</v>
       </c>
       <c r="T6">
-        <v>0.8277094634564007</v>
+        <v>0.8338824511446543</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>162.1555582704888</v>
+        <v>129.724446616391</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.158887546301345</v>
+        <v>0.1584356045359602</v>
       </c>
       <c r="C7">
-        <v>1.755994271471982</v>
+        <v>1.743722087806675</v>
       </c>
       <c r="D7">
-        <v>1.781494271471982</v>
+        <v>1.787122087806675</v>
       </c>
       <c r="E7">
-        <v>-0.2605</v>
+        <v>-0.2426</v>
       </c>
       <c r="F7">
-        <v>0.08950000000000001</v>
+        <v>0.1074</v>
       </c>
       <c r="G7">
         <v>0.064</v>
@@ -1861,28 +1861,28 @@
         <v>0.584</v>
       </c>
       <c r="M7">
-        <v>0.00450185</v>
+        <v>0.00540222</v>
       </c>
       <c r="N7">
-        <v>0.5794981499999999</v>
+        <v>0.57859778</v>
       </c>
       <c r="O7">
-        <v>0.173849445</v>
+        <v>0.173579334</v>
       </c>
       <c r="P7">
-        <v>0.4056487049999999</v>
+        <v>0.405018446</v>
       </c>
       <c r="Q7">
-        <v>0.4116487049999999</v>
+        <v>0.411018446</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.165396890843521</v>
+        <v>0.1663010686552768</v>
       </c>
       <c r="T7">
-        <v>0.8338824511446543</v>
+        <v>0.8401867789964877</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>129.724446616391</v>
+        <v>108.1037055136592</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1584356045359602</v>
+        <v>0.1579836627705754</v>
       </c>
       <c r="C8">
-        <v>1.743722087806675</v>
+        <v>1.73148557384683</v>
       </c>
       <c r="D8">
-        <v>1.787122087806675</v>
+        <v>1.79278557384683</v>
       </c>
       <c r="E8">
-        <v>-0.2426</v>
+        <v>-0.2247</v>
       </c>
       <c r="F8">
-        <v>0.1074</v>
+        <v>0.1253</v>
       </c>
       <c r="G8">
         <v>0.064</v>
@@ -1943,28 +1943,28 @@
         <v>0.584</v>
       </c>
       <c r="M8">
-        <v>0.005402219999999999</v>
+        <v>0.006302589999999999</v>
       </c>
       <c r="N8">
-        <v>0.57859778</v>
+        <v>0.57769741</v>
       </c>
       <c r="O8">
-        <v>0.173579334</v>
+        <v>0.173309223</v>
       </c>
       <c r="P8">
-        <v>0.405018446</v>
+        <v>0.404388187</v>
       </c>
       <c r="Q8">
-        <v>0.411018446</v>
+        <v>0.410388187</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1663010686552768</v>
+        <v>0.1672246911511563</v>
       </c>
       <c r="T8">
-        <v>0.8401867789964877</v>
+        <v>0.8466266837913715</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>108.1037055136592</v>
+        <v>92.66031901170788</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1579836627705754</v>
+        <v>0.1575317210051906</v>
       </c>
       <c r="C9">
-        <v>1.73148557384683</v>
+        <v>1.719285069788192</v>
       </c>
       <c r="D9">
-        <v>1.79278557384683</v>
+        <v>1.798485069788192</v>
       </c>
       <c r="E9">
-        <v>-0.2247</v>
+        <v>-0.2068</v>
       </c>
       <c r="F9">
-        <v>0.1253</v>
+        <v>0.1432</v>
       </c>
       <c r="G9">
         <v>0.064</v>
@@ -2025,28 +2025,28 @@
         <v>0.584</v>
       </c>
       <c r="M9">
-        <v>0.006302590000000001</v>
+        <v>0.00720296</v>
       </c>
       <c r="N9">
-        <v>0.57769741</v>
+        <v>0.57679704</v>
       </c>
       <c r="O9">
-        <v>0.173309223</v>
+        <v>0.173039112</v>
       </c>
       <c r="P9">
-        <v>0.404388187</v>
+        <v>0.403757928</v>
       </c>
       <c r="Q9">
-        <v>0.410388187</v>
+        <v>0.409757928</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1672246911511563</v>
+        <v>0.1681683923969463</v>
       </c>
       <c r="T9">
-        <v>0.8466266837913715</v>
+        <v>0.8532065865165788</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>92.66031901170787</v>
+        <v>81.0777791352444</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1575317210051906</v>
+        <v>0.1570797792398058</v>
       </c>
       <c r="C10">
-        <v>1.719285069788192</v>
+        <v>1.707120920166408</v>
       </c>
       <c r="D10">
-        <v>1.798485069788192</v>
+        <v>1.804220920166408</v>
       </c>
       <c r="E10">
-        <v>-0.2068</v>
+        <v>-0.1889</v>
       </c>
       <c r="F10">
-        <v>0.1432</v>
+        <v>0.1611</v>
       </c>
       <c r="G10">
         <v>0.064</v>
@@ -2107,28 +2107,28 @@
         <v>0.584</v>
       </c>
       <c r="M10">
-        <v>0.00720296</v>
+        <v>0.008103329999999999</v>
       </c>
       <c r="N10">
-        <v>0.57679704</v>
+        <v>0.57589667</v>
       </c>
       <c r="O10">
-        <v>0.173039112</v>
+        <v>0.172769001</v>
       </c>
       <c r="P10">
-        <v>0.403757928</v>
+        <v>0.403127669</v>
       </c>
       <c r="Q10">
-        <v>0.409757928</v>
+        <v>0.409127669</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1681683923969463</v>
+        <v>0.1691328343294569</v>
       </c>
       <c r="T10">
-        <v>0.8532065865165788</v>
+        <v>0.8599311024884937</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>81.0777791352444</v>
+        <v>72.06913700910614</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1570797792398058</v>
+        <v>0.156627837474421</v>
       </c>
       <c r="C11">
-        <v>1.707120920166408</v>
+        <v>1.694993473926452</v>
       </c>
       <c r="D11">
-        <v>1.804220920166408</v>
+        <v>1.809993473926452</v>
       </c>
       <c r="E11">
-        <v>-0.1889</v>
+        <v>-0.171</v>
       </c>
       <c r="F11">
-        <v>0.1611</v>
+        <v>0.179</v>
       </c>
       <c r="G11">
         <v>0.064</v>
@@ -2189,28 +2189,28 @@
         <v>0.584</v>
       </c>
       <c r="M11">
-        <v>0.008103329999999999</v>
+        <v>0.0090037</v>
       </c>
       <c r="N11">
-        <v>0.57589667</v>
+        <v>0.5749963</v>
       </c>
       <c r="O11">
-        <v>0.172769001</v>
+        <v>0.17249889</v>
       </c>
       <c r="P11">
-        <v>0.403127669</v>
+        <v>0.4024974100000001</v>
       </c>
       <c r="Q11">
-        <v>0.409127669</v>
+        <v>0.4084974100000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1691328343294569</v>
+        <v>0.1701187083049122</v>
       </c>
       <c r="T11">
-        <v>0.8599311024884937</v>
+        <v>0.8668050521486734</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>72.06913700910614</v>
+        <v>64.86222330819552</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.156627837474421</v>
+        <v>0.1561758957090362</v>
       </c>
       <c r="C12">
-        <v>1.694993473926452</v>
+        <v>1.682903084493392</v>
       </c>
       <c r="D12">
-        <v>1.809993473926452</v>
+        <v>1.815803084493392</v>
       </c>
       <c r="E12">
-        <v>-0.171</v>
+        <v>-0.1531</v>
       </c>
       <c r="F12">
-        <v>0.179</v>
+        <v>0.1969</v>
       </c>
       <c r="G12">
         <v>0.064</v>
@@ -2271,28 +2271,28 @@
         <v>0.584</v>
       </c>
       <c r="M12">
-        <v>0.0090037</v>
+        <v>0.009904069999999999</v>
       </c>
       <c r="N12">
-        <v>0.5749963</v>
+        <v>0.5740959299999999</v>
       </c>
       <c r="O12">
-        <v>0.17249889</v>
+        <v>0.172228779</v>
       </c>
       <c r="P12">
-        <v>0.4024974100000001</v>
+        <v>0.4018671509999999</v>
       </c>
       <c r="Q12">
-        <v>0.4084974100000001</v>
+        <v>0.4078671509999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1701187083049122</v>
+        <v>0.171126736751726</v>
       </c>
       <c r="T12">
-        <v>0.8668050521486734</v>
+        <v>0.8738334725877337</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>64.86222330819552</v>
+        <v>58.96565755290501</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1561758957090362</v>
+        <v>0.1557239539436514</v>
       </c>
       <c r="C13">
-        <v>1.682903084493392</v>
+        <v>1.670850109844518</v>
       </c>
       <c r="D13">
-        <v>1.815803084493392</v>
+        <v>1.821650109844517</v>
       </c>
       <c r="E13">
-        <v>-0.1531</v>
+        <v>-0.1352</v>
       </c>
       <c r="F13">
-        <v>0.1969</v>
+        <v>0.2148</v>
       </c>
       <c r="G13">
         <v>0.064</v>
@@ -2353,28 +2353,28 @@
         <v>0.584</v>
       </c>
       <c r="M13">
-        <v>0.009904069999999999</v>
+        <v>0.01080444</v>
       </c>
       <c r="N13">
-        <v>0.5740959299999999</v>
+        <v>0.5731955599999999</v>
       </c>
       <c r="O13">
-        <v>0.172228779</v>
+        <v>0.171958668</v>
       </c>
       <c r="P13">
-        <v>0.4018671509999999</v>
+        <v>0.401236892</v>
       </c>
       <c r="Q13">
-        <v>0.4078671509999999</v>
+        <v>0.407236892</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.171126736751726</v>
+        <v>0.1721576749359675</v>
       </c>
       <c r="T13">
-        <v>0.8738334725877337</v>
+        <v>0.8810216298549545</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>58.96565755290501</v>
+        <v>54.0518527568296</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1557239539436514</v>
+        <v>0.1552720121782666</v>
       </c>
       <c r="C14">
-        <v>1.670850109844518</v>
+        <v>1.658834912582872</v>
       </c>
       <c r="D14">
-        <v>1.821650109844517</v>
+        <v>1.827534912582872</v>
       </c>
       <c r="E14">
-        <v>-0.1352</v>
+        <v>-0.1173</v>
       </c>
       <c r="F14">
-        <v>0.2148</v>
+        <v>0.2327</v>
       </c>
       <c r="G14">
         <v>0.064</v>
@@ -2435,28 +2435,28 @@
         <v>0.584</v>
       </c>
       <c r="M14">
-        <v>0.01080444</v>
+        <v>0.01170481</v>
       </c>
       <c r="N14">
-        <v>0.5731955599999999</v>
+        <v>0.57229519</v>
       </c>
       <c r="O14">
-        <v>0.171958668</v>
+        <v>0.171688557</v>
       </c>
       <c r="P14">
-        <v>0.401236892</v>
+        <v>0.400606633</v>
       </c>
       <c r="Q14">
-        <v>0.407236892</v>
+        <v>0.406606633</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1721576749359675</v>
+        <v>0.1732123128485822</v>
       </c>
       <c r="T14">
-        <v>0.8810216298549545</v>
+        <v>0.8883750321168239</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>54.0518527568296</v>
+        <v>49.89401792938116</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1552720121782666</v>
+        <v>0.1548200704128817</v>
       </c>
       <c r="C15">
-        <v>1.658834912582872</v>
+        <v>1.64685786001221</v>
       </c>
       <c r="D15">
-        <v>1.827534912582872</v>
+        <v>1.83345786001221</v>
       </c>
       <c r="E15">
-        <v>-0.1173</v>
+        <v>-0.09939999999999993</v>
       </c>
       <c r="F15">
-        <v>0.2327</v>
+        <v>0.2506</v>
       </c>
       <c r="G15">
         <v>0.064</v>
@@ -2517,28 +2517,28 @@
         <v>0.584</v>
       </c>
       <c r="M15">
-        <v>0.01170481</v>
+        <v>0.01260518</v>
       </c>
       <c r="N15">
-        <v>0.57229519</v>
+        <v>0.57139482</v>
       </c>
       <c r="O15">
-        <v>0.171688557</v>
+        <v>0.171418446</v>
       </c>
       <c r="P15">
-        <v>0.400606633</v>
+        <v>0.399976374</v>
       </c>
       <c r="Q15">
-        <v>0.406606633</v>
+        <v>0.405976374</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1732123128485822</v>
+        <v>0.1742914772242811</v>
       </c>
       <c r="T15">
-        <v>0.8883750321168239</v>
+        <v>0.8958994437336205</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>49.89401792938116</v>
+        <v>46.33015950585393</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1548200704128817</v>
+        <v>0.154368128647497</v>
       </c>
       <c r="C16">
-        <v>1.64685786001221</v>
+        <v>1.63491932421342</v>
       </c>
       <c r="D16">
-        <v>1.83345786001221</v>
+        <v>1.83941932421342</v>
       </c>
       <c r="E16">
-        <v>-0.09939999999999993</v>
+        <v>-0.08149999999999991</v>
       </c>
       <c r="F16">
-        <v>0.2506</v>
+        <v>0.2685000000000001</v>
       </c>
       <c r="G16">
         <v>0.064</v>
@@ -2599,28 +2599,28 @@
         <v>0.584</v>
       </c>
       <c r="M16">
-        <v>0.01260518</v>
+        <v>0.01350555</v>
       </c>
       <c r="N16">
-        <v>0.57139482</v>
+        <v>0.57049445</v>
       </c>
       <c r="O16">
-        <v>0.171418446</v>
+        <v>0.171148335</v>
       </c>
       <c r="P16">
-        <v>0.399976374</v>
+        <v>0.399346115</v>
       </c>
       <c r="Q16">
-        <v>0.405976374</v>
+        <v>0.405346115</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1742914772242811</v>
+        <v>0.1753960337029376</v>
       </c>
       <c r="T16">
-        <v>0.8958994437336205</v>
+        <v>0.903600900329636</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>46.33015950585393</v>
+        <v>43.24148220546367</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.154368128647497</v>
+        <v>0.1539161868821121</v>
       </c>
       <c r="C17">
-        <v>1.63491932421342</v>
+        <v>1.623019682122442</v>
       </c>
       <c r="D17">
-        <v>1.83941932421342</v>
+        <v>1.845419682122442</v>
       </c>
       <c r="E17">
-        <v>-0.08149999999999996</v>
+        <v>-0.06359999999999999</v>
       </c>
       <c r="F17">
-        <v>0.2685</v>
+        <v>0.2864</v>
       </c>
       <c r="G17">
         <v>0.064</v>
@@ -2681,28 +2681,28 @@
         <v>0.584</v>
       </c>
       <c r="M17">
-        <v>0.01350555</v>
+        <v>0.01440592</v>
       </c>
       <c r="N17">
-        <v>0.57049445</v>
+        <v>0.56959408</v>
       </c>
       <c r="O17">
-        <v>0.171148335</v>
+        <v>0.170878224</v>
       </c>
       <c r="P17">
-        <v>0.399346115</v>
+        <v>0.398715856</v>
       </c>
       <c r="Q17">
-        <v>0.405346115</v>
+        <v>0.404715856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1753960337029376</v>
+        <v>0.1765268891453716</v>
       </c>
       <c r="T17">
-        <v>0.903600900329636</v>
+        <v>0.9114857249398423</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>43.24148220546368</v>
+        <v>40.5388895676222</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1539161868821121</v>
+        <v>0.1534642451167273</v>
       </c>
       <c r="C18">
-        <v>1.623019682122442</v>
+        <v>1.611159315609711</v>
       </c>
       <c r="D18">
-        <v>1.845419682122442</v>
+        <v>1.851459315609711</v>
       </c>
       <c r="E18">
-        <v>-0.06359999999999999</v>
+        <v>-0.04569999999999996</v>
       </c>
       <c r="F18">
-        <v>0.2864</v>
+        <v>0.3043</v>
       </c>
       <c r="G18">
         <v>0.064</v>
@@ -2763,28 +2763,28 @@
         <v>0.584</v>
       </c>
       <c r="M18">
-        <v>0.01440592</v>
+        <v>0.01530629</v>
       </c>
       <c r="N18">
-        <v>0.56959408</v>
+        <v>0.56869371</v>
       </c>
       <c r="O18">
-        <v>0.170878224</v>
+        <v>0.170608113</v>
       </c>
       <c r="P18">
-        <v>0.398715856</v>
+        <v>0.398085597</v>
       </c>
       <c r="Q18">
-        <v>0.404715856</v>
+        <v>0.404085597</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1765268891453716</v>
+        <v>0.177684994116539</v>
       </c>
       <c r="T18">
-        <v>0.9114857249398423</v>
+        <v>0.9195605453237885</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>40.5388895676222</v>
+        <v>38.1542490048209</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1534642451167273</v>
+        <v>0.1530123033513425</v>
       </c>
       <c r="C19">
-        <v>1.611159315609711</v>
+        <v>1.599338611561177</v>
       </c>
       <c r="D19">
-        <v>1.851459315609711</v>
+        <v>1.857538611561177</v>
       </c>
       <c r="E19">
-        <v>-0.04569999999999996</v>
+        <v>-0.02779999999999994</v>
       </c>
       <c r="F19">
-        <v>0.3043</v>
+        <v>0.3222</v>
       </c>
       <c r="G19">
         <v>0.064</v>
@@ -2845,28 +2845,28 @@
         <v>0.584</v>
       </c>
       <c r="M19">
-        <v>0.01530629</v>
+        <v>0.01620666</v>
       </c>
       <c r="N19">
-        <v>0.56869371</v>
+        <v>0.5677933399999999</v>
       </c>
       <c r="O19">
-        <v>0.170608113</v>
+        <v>0.170338002</v>
       </c>
       <c r="P19">
-        <v>0.398085597</v>
+        <v>0.397455338</v>
       </c>
       <c r="Q19">
-        <v>0.404085597</v>
+        <v>0.403455338</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.177684994116539</v>
+        <v>0.1788713455504177</v>
       </c>
       <c r="T19">
-        <v>0.9195605453237885</v>
+        <v>0.9278323125463673</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>38.1542490048209</v>
+        <v>36.03456850455306</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1530123033513425</v>
+        <v>0.1525603615859577</v>
       </c>
       <c r="C20">
-        <v>1.599338611561176</v>
+        <v>1.587557961960909</v>
       </c>
       <c r="D20">
-        <v>1.857538611561176</v>
+        <v>1.863657961960909</v>
       </c>
       <c r="E20">
-        <v>-0.02779999999999999</v>
+        <v>-0.009899999999999964</v>
       </c>
       <c r="F20">
-        <v>0.3222</v>
+        <v>0.3401</v>
       </c>
       <c r="G20">
         <v>0.064</v>
@@ -2927,28 +2927,28 @@
         <v>0.584</v>
       </c>
       <c r="M20">
-        <v>0.01620666</v>
+        <v>0.01710703</v>
       </c>
       <c r="N20">
-        <v>0.5677933399999999</v>
+        <v>0.5668929699999999</v>
       </c>
       <c r="O20">
-        <v>0.170338002</v>
+        <v>0.170067891</v>
       </c>
       <c r="P20">
-        <v>0.397455338</v>
+        <v>0.396825079</v>
       </c>
       <c r="Q20">
-        <v>0.403455338</v>
+        <v>0.402825079</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1788713455504177</v>
+        <v>0.1800869896122935</v>
       </c>
       <c r="T20">
-        <v>0.9278323125463673</v>
+        <v>0.9363083209349359</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>36.03456850455306</v>
+        <v>34.13801226747132</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1525603615859577</v>
+        <v>0.1521084198205729</v>
       </c>
       <c r="C21">
-        <v>1.587557961960909</v>
+        <v>1.575817763975357</v>
       </c>
       <c r="D21">
-        <v>1.863657961960909</v>
+        <v>1.869817763975357</v>
       </c>
       <c r="E21">
-        <v>-0.009899999999999964</v>
+        <v>0.008000000000000063</v>
       </c>
       <c r="F21">
-        <v>0.3401</v>
+        <v>0.358</v>
       </c>
       <c r="G21">
         <v>0.064</v>
@@ -3009,28 +3009,28 @@
         <v>0.584</v>
       </c>
       <c r="M21">
-        <v>0.01710703</v>
+        <v>0.0180074</v>
       </c>
       <c r="N21">
-        <v>0.5668929699999999</v>
+        <v>0.5659926</v>
       </c>
       <c r="O21">
-        <v>0.170067891</v>
+        <v>0.16979778</v>
       </c>
       <c r="P21">
-        <v>0.396825079</v>
+        <v>0.3961948199999999</v>
       </c>
       <c r="Q21">
-        <v>0.402825079</v>
+        <v>0.40219482</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1800869896122935</v>
+        <v>0.1813330247757161</v>
       </c>
       <c r="T21">
-        <v>0.9363083209349359</v>
+        <v>0.9449962295332188</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>34.13801226747132</v>
+        <v>32.43111165409776</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1521084198205729</v>
+        <v>0.1516564780551881</v>
       </c>
       <c r="C22">
-        <v>1.575817763975357</v>
+        <v>1.564118420039273</v>
       </c>
       <c r="D22">
-        <v>1.869817763975357</v>
+        <v>1.876018420039273</v>
       </c>
       <c r="E22">
-        <v>0.008000000000000063</v>
+        <v>0.02590000000000009</v>
       </c>
       <c r="F22">
-        <v>0.358</v>
+        <v>0.3759000000000001</v>
       </c>
       <c r="G22">
         <v>0.064</v>
@@ -3091,28 +3091,28 @@
         <v>0.584</v>
       </c>
       <c r="M22">
-        <v>0.0180074</v>
+        <v>0.01890777</v>
       </c>
       <c r="N22">
-        <v>0.5659926</v>
+        <v>0.56509223</v>
       </c>
       <c r="O22">
-        <v>0.16979778</v>
+        <v>0.169527669</v>
       </c>
       <c r="P22">
-        <v>0.3961948199999999</v>
+        <v>0.395564561</v>
       </c>
       <c r="Q22">
-        <v>0.40219482</v>
+        <v>0.401564561</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1813330247757161</v>
+        <v>0.1826106051331495</v>
       </c>
       <c r="T22">
-        <v>0.9449962295332188</v>
+        <v>0.9539040851846228</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>32.43111165409776</v>
+        <v>30.88677300390263</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1516564780551881</v>
+        <v>0.1512045362898033</v>
       </c>
       <c r="C23">
-        <v>1.564118420039273</v>
+        <v>1.55246033794336</v>
       </c>
       <c r="D23">
-        <v>1.876018420039273</v>
+        <v>1.88226033794336</v>
       </c>
       <c r="E23">
-        <v>0.02590000000000003</v>
+        <v>0.04380000000000001</v>
       </c>
       <c r="F23">
-        <v>0.3759</v>
+        <v>0.3938</v>
       </c>
       <c r="G23">
         <v>0.064</v>
@@ -3173,28 +3173,28 @@
         <v>0.584</v>
       </c>
       <c r="M23">
-        <v>0.01890777</v>
+        <v>0.01980814</v>
       </c>
       <c r="N23">
-        <v>0.56509223</v>
+        <v>0.56419186</v>
       </c>
       <c r="O23">
-        <v>0.169527669</v>
+        <v>0.169257558</v>
       </c>
       <c r="P23">
-        <v>0.395564561</v>
+        <v>0.394934302</v>
       </c>
       <c r="Q23">
-        <v>0.401564561</v>
+        <v>0.400934302</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1826106051331495</v>
+        <v>0.1839209439612863</v>
       </c>
       <c r="T23">
-        <v>0.9539040851846226</v>
+        <v>0.9630403473911907</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>30.88677300390263</v>
+        <v>29.48282877645251</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1512045362898033</v>
+        <v>0.1507525945244185</v>
       </c>
       <c r="C24">
-        <v>1.55246033794336</v>
+        <v>1.540843930923669</v>
       </c>
       <c r="D24">
-        <v>1.88226033794336</v>
+        <v>1.888543930923668</v>
       </c>
       <c r="E24">
-        <v>0.04380000000000001</v>
+        <v>0.06170000000000003</v>
       </c>
       <c r="F24">
-        <v>0.3938</v>
+        <v>0.4117</v>
       </c>
       <c r="G24">
         <v>0.064</v>
@@ -3255,28 +3255,28 @@
         <v>0.584</v>
       </c>
       <c r="M24">
-        <v>0.01980814</v>
+        <v>0.02070851</v>
       </c>
       <c r="N24">
-        <v>0.56419186</v>
+        <v>0.56329149</v>
       </c>
       <c r="O24">
-        <v>0.169257558</v>
+        <v>0.168987447</v>
       </c>
       <c r="P24">
-        <v>0.394934302</v>
+        <v>0.394304043</v>
       </c>
       <c r="Q24">
-        <v>0.400934302</v>
+        <v>0.400304043</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1839209439612863</v>
+        <v>0.1852653175641799</v>
       </c>
       <c r="T24">
-        <v>0.9630403473911907</v>
+        <v>0.9724139151096177</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>29.48282877645251</v>
+        <v>28.20096665573718</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1507525945244185</v>
+        <v>0.1503006527590337</v>
       </c>
       <c r="C25">
-        <v>1.540843930923669</v>
+        <v>1.529269617752793</v>
       </c>
       <c r="D25">
-        <v>1.888543930923668</v>
+        <v>1.894869617752793</v>
       </c>
       <c r="E25">
-        <v>0.06170000000000003</v>
+        <v>0.07960000000000006</v>
       </c>
       <c r="F25">
-        <v>0.4117</v>
+        <v>0.4296</v>
       </c>
       <c r="G25">
         <v>0.064</v>
@@ -3337,28 +3337,28 @@
         <v>0.584</v>
       </c>
       <c r="M25">
-        <v>0.02070851</v>
+        <v>0.02160888</v>
       </c>
       <c r="N25">
-        <v>0.56329149</v>
+        <v>0.5623911199999999</v>
       </c>
       <c r="O25">
-        <v>0.168987447</v>
+        <v>0.168717336</v>
       </c>
       <c r="P25">
-        <v>0.394304043</v>
+        <v>0.393673784</v>
       </c>
       <c r="Q25">
-        <v>0.400304043</v>
+        <v>0.399673784</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1852653175641799</v>
+        <v>0.1866450694197812</v>
       </c>
       <c r="T25">
-        <v>0.9724139151096177</v>
+        <v>0.9820341556627402</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>28.20096665573718</v>
+        <v>27.02592637841479</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1503006527590337</v>
+        <v>0.1498487109936489</v>
       </c>
       <c r="C26">
-        <v>1.529269617752793</v>
+        <v>1.517737822832907</v>
       </c>
       <c r="D26">
-        <v>1.894869617752793</v>
+        <v>1.901237822832907</v>
       </c>
       <c r="E26">
-        <v>0.0796</v>
+        <v>0.09750000000000003</v>
       </c>
       <c r="F26">
-        <v>0.4296</v>
+        <v>0.4475</v>
       </c>
       <c r="G26">
         <v>0.064</v>
@@ -3419,28 +3419,28 @@
         <v>0.584</v>
       </c>
       <c r="M26">
-        <v>0.02160888</v>
+        <v>0.02250925</v>
       </c>
       <c r="N26">
-        <v>0.56239112</v>
+        <v>0.5614907499999999</v>
       </c>
       <c r="O26">
-        <v>0.168717336</v>
+        <v>0.168447225</v>
       </c>
       <c r="P26">
-        <v>0.393673784</v>
+        <v>0.3930435249999999</v>
       </c>
       <c r="Q26">
-        <v>0.399673784</v>
+        <v>0.399043525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1866450694197812</v>
+        <v>0.1880616146581985</v>
       </c>
       <c r="T26">
-        <v>0.9820341556627402</v>
+        <v>0.991910935963946</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>27.02592637841481</v>
+        <v>25.94488932327821</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1498487109936489</v>
+        <v>0.1493967692282641</v>
       </c>
       <c r="C27">
-        <v>1.517737822832907</v>
+        <v>1.506248976290681</v>
       </c>
       <c r="D27">
-        <v>1.901237822832907</v>
+        <v>1.907648976290681</v>
       </c>
       <c r="E27">
-        <v>0.09750000000000003</v>
+        <v>0.1154000000000001</v>
       </c>
       <c r="F27">
-        <v>0.4475</v>
+        <v>0.4654</v>
       </c>
       <c r="G27">
         <v>0.064</v>
@@ -3501,28 +3501,28 @@
         <v>0.584</v>
       </c>
       <c r="M27">
-        <v>0.02250925</v>
+        <v>0.02340962</v>
       </c>
       <c r="N27">
-        <v>0.5614907499999999</v>
+        <v>0.5605903799999999</v>
       </c>
       <c r="O27">
-        <v>0.168447225</v>
+        <v>0.168177114</v>
       </c>
       <c r="P27">
-        <v>0.3930435249999999</v>
+        <v>0.3924132659999999</v>
       </c>
       <c r="Q27">
-        <v>0.399043525</v>
+        <v>0.3984132659999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1880616146581985</v>
+        <v>0.1895164449030595</v>
       </c>
       <c r="T27">
-        <v>0.991910935963946</v>
+        <v>1.002054656273292</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>25.94488932327821</v>
+        <v>24.94700896469058</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1493967692282641</v>
+        <v>0.1489448274628793</v>
       </c>
       <c r="C28">
-        <v>1.506248976290681</v>
+        <v>1.49480351407413</v>
       </c>
       <c r="D28">
-        <v>1.907648976290681</v>
+        <v>1.91410351407413</v>
       </c>
       <c r="E28">
-        <v>0.1154000000000001</v>
+        <v>0.1333000000000001</v>
       </c>
       <c r="F28">
-        <v>0.4654</v>
+        <v>0.4833000000000001</v>
       </c>
       <c r="G28">
         <v>0.064</v>
@@ -3583,28 +3583,28 @@
         <v>0.584</v>
       </c>
       <c r="M28">
-        <v>0.02340962</v>
+        <v>0.02430999</v>
       </c>
       <c r="N28">
-        <v>0.5605903799999999</v>
+        <v>0.55969001</v>
       </c>
       <c r="O28">
-        <v>0.168177114</v>
+        <v>0.167907003</v>
       </c>
       <c r="P28">
-        <v>0.3924132659999999</v>
+        <v>0.391783007</v>
       </c>
       <c r="Q28">
-        <v>0.3984132659999999</v>
+        <v>0.397783007</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1895164449030595</v>
+        <v>0.1910111335107935</v>
       </c>
       <c r="T28">
-        <v>1.002054656273292</v>
+        <v>1.012476286728101</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>24.94700896469058</v>
+        <v>24.02304566970204</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1489448274628793</v>
+        <v>0.1484928856974944</v>
       </c>
       <c r="C29">
-        <v>1.49480351407413</v>
+        <v>1.483401878051422</v>
       </c>
       <c r="D29">
-        <v>1.91410351407413</v>
+        <v>1.920601878051422</v>
       </c>
       <c r="E29">
-        <v>0.1333000000000001</v>
+        <v>0.1512000000000001</v>
       </c>
       <c r="F29">
-        <v>0.4833000000000001</v>
+        <v>0.5012000000000001</v>
       </c>
       <c r="G29">
         <v>0.064</v>
@@ -3665,28 +3665,28 @@
         <v>0.584</v>
       </c>
       <c r="M29">
-        <v>0.02430999</v>
+        <v>0.02521036</v>
       </c>
       <c r="N29">
-        <v>0.55969001</v>
+        <v>0.55878964</v>
       </c>
       <c r="O29">
-        <v>0.167907003</v>
+        <v>0.167636892</v>
       </c>
       <c r="P29">
-        <v>0.391783007</v>
+        <v>0.391152748</v>
       </c>
       <c r="Q29">
-        <v>0.397783007</v>
+        <v>0.397152748</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1910111335107935</v>
+        <v>0.1925473412465201</v>
       </c>
       <c r="T29">
-        <v>1.012476286728101</v>
+        <v>1.023187406917764</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>24.02304566970204</v>
+        <v>23.16507975292697</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1484928856974944</v>
+        <v>0.1480409439321096</v>
       </c>
       <c r="C30">
-        <v>1.483401878051422</v>
+        <v>1.472044516111721</v>
       </c>
       <c r="D30">
-        <v>1.920601878051422</v>
+        <v>1.927144516111722</v>
       </c>
       <c r="E30">
-        <v>0.1512000000000001</v>
+        <v>0.1691000000000001</v>
       </c>
       <c r="F30">
-        <v>0.5012000000000001</v>
+        <v>0.5191000000000001</v>
       </c>
       <c r="G30">
         <v>0.064</v>
@@ -3747,28 +3747,28 @@
         <v>0.584</v>
       </c>
       <c r="M30">
-        <v>0.02521036</v>
+        <v>0.02611073000000001</v>
       </c>
       <c r="N30">
-        <v>0.55878964</v>
+        <v>0.55788927</v>
       </c>
       <c r="O30">
-        <v>0.167636892</v>
+        <v>0.167366781</v>
       </c>
       <c r="P30">
-        <v>0.391152748</v>
+        <v>0.390522489</v>
       </c>
       <c r="Q30">
-        <v>0.397152748</v>
+        <v>0.396522489</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1925473412465201</v>
+        <v>0.1941268224395911</v>
       </c>
       <c r="T30">
-        <v>1.023187406917764</v>
+        <v>1.034200248802911</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>23.16507975292697</v>
+        <v>22.36628389937776</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1480409439321096</v>
+        <v>0.1475890021667248</v>
       </c>
       <c r="C31">
-        <v>1.472044516111722</v>
+        <v>1.460731882268095</v>
       </c>
       <c r="D31">
-        <v>1.927144516111722</v>
+        <v>1.933731882268095</v>
       </c>
       <c r="E31">
-        <v>0.1691</v>
+        <v>0.1870000000000001</v>
       </c>
       <c r="F31">
-        <v>0.5191</v>
+        <v>0.537</v>
       </c>
       <c r="G31">
         <v>0.064</v>
@@ -3829,28 +3829,28 @@
         <v>0.584</v>
       </c>
       <c r="M31">
-        <v>0.02611073</v>
+        <v>0.0270111</v>
       </c>
       <c r="N31">
-        <v>0.55788927</v>
+        <v>0.5569889</v>
       </c>
       <c r="O31">
-        <v>0.167366781</v>
+        <v>0.16709667</v>
       </c>
       <c r="P31">
-        <v>0.390522489</v>
+        <v>0.38989223</v>
       </c>
       <c r="Q31">
-        <v>0.396522489</v>
+        <v>0.39589223</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1941268224395911</v>
+        <v>0.1957514316667498</v>
       </c>
       <c r="T31">
-        <v>1.034200248802911</v>
+        <v>1.045527743313349</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>22.36628389937777</v>
+        <v>21.62074110273184</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1475890021667248</v>
+        <v>0.14713706040134</v>
       </c>
       <c r="C32">
-        <v>1.460731882268095</v>
+        <v>1.449464436762528</v>
       </c>
       <c r="D32">
-        <v>1.933731882268095</v>
+        <v>1.940364436762528</v>
       </c>
       <c r="E32">
-        <v>0.1870000000000001</v>
+        <v>0.2049000000000001</v>
       </c>
       <c r="F32">
-        <v>0.537</v>
+        <v>0.5549000000000001</v>
       </c>
       <c r="G32">
         <v>0.064</v>
@@ -3911,28 +3911,28 @@
         <v>0.584</v>
       </c>
       <c r="M32">
-        <v>0.0270111</v>
+        <v>0.02791147</v>
       </c>
       <c r="N32">
-        <v>0.5569889</v>
+        <v>0.5560885299999999</v>
       </c>
       <c r="O32">
-        <v>0.16709667</v>
+        <v>0.166826559</v>
       </c>
       <c r="P32">
-        <v>0.38989223</v>
+        <v>0.3892619709999999</v>
       </c>
       <c r="Q32">
-        <v>0.39589223</v>
+        <v>0.3952619709999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1957514316667498</v>
+        <v>0.1974231310164348</v>
       </c>
       <c r="T32">
-        <v>1.045527743313349</v>
+        <v>1.057183570998001</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.62074110273184</v>
+        <v>20.92329784135339</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.14713706040134</v>
+        <v>0.1466851186359552</v>
       </c>
       <c r="C33">
-        <v>1.449464436762528</v>
+        <v>1.438242646173123</v>
       </c>
       <c r="D33">
-        <v>1.940364436762528</v>
+        <v>1.947042646173123</v>
       </c>
       <c r="E33">
-        <v>0.2049000000000001</v>
+        <v>0.2228</v>
       </c>
       <c r="F33">
-        <v>0.5549000000000001</v>
+        <v>0.5728</v>
       </c>
       <c r="G33">
         <v>0.064</v>
@@ -3993,28 +3993,28 @@
         <v>0.584</v>
       </c>
       <c r="M33">
-        <v>0.02791147</v>
+        <v>0.02881184</v>
       </c>
       <c r="N33">
-        <v>0.5560885299999999</v>
+        <v>0.5551881599999999</v>
       </c>
       <c r="O33">
-        <v>0.166826559</v>
+        <v>0.166556448</v>
       </c>
       <c r="P33">
-        <v>0.3892619709999999</v>
+        <v>0.388631712</v>
       </c>
       <c r="Q33">
-        <v>0.3952619709999999</v>
+        <v>0.394631712</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1974231310164348</v>
+        <v>0.1991439979940518</v>
       </c>
       <c r="T33">
-        <v>1.057183570998001</v>
+        <v>1.069182217143967</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>20.92329784135339</v>
+        <v>20.2694447838111</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1466851186359552</v>
+        <v>0.1462331768705704</v>
       </c>
       <c r="C34">
-        <v>1.438242646173123</v>
+        <v>1.427066983523504</v>
       </c>
       <c r="D34">
-        <v>1.947042646173123</v>
+        <v>1.953766983523505</v>
       </c>
       <c r="E34">
-        <v>0.2228</v>
+        <v>0.2407</v>
       </c>
       <c r="F34">
-        <v>0.5728</v>
+        <v>0.5907</v>
       </c>
       <c r="G34">
         <v>0.064</v>
@@ -4075,28 +4075,28 @@
         <v>0.584</v>
       </c>
       <c r="M34">
-        <v>0.02881184</v>
+        <v>0.02971221</v>
       </c>
       <c r="N34">
-        <v>0.5551881599999999</v>
+        <v>0.5542877899999999</v>
       </c>
       <c r="O34">
-        <v>0.166556448</v>
+        <v>0.166286337</v>
       </c>
       <c r="P34">
-        <v>0.388631712</v>
+        <v>0.388001453</v>
       </c>
       <c r="Q34">
-        <v>0.394631712</v>
+        <v>0.394001453</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1991439979940518</v>
+        <v>0.2009162341351798</v>
       </c>
       <c r="T34">
-        <v>1.069182217143967</v>
+        <v>1.081539031831604</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>20.2694447838111</v>
+        <v>19.65521918430167</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1462331768705704</v>
+        <v>0.1457812351051856</v>
       </c>
       <c r="C35">
-        <v>1.427066983523504</v>
+        <v>1.415937928394515</v>
       </c>
       <c r="D35">
-        <v>1.953766983523505</v>
+        <v>1.960537928394515</v>
       </c>
       <c r="E35">
-        <v>0.2407</v>
+        <v>0.2586000000000001</v>
       </c>
       <c r="F35">
-        <v>0.5907</v>
+        <v>0.6086</v>
       </c>
       <c r="G35">
         <v>0.064</v>
@@ -4157,28 +4157,28 @@
         <v>0.584</v>
       </c>
       <c r="M35">
-        <v>0.02971221</v>
+        <v>0.03061258</v>
       </c>
       <c r="N35">
-        <v>0.5542877899999999</v>
+        <v>0.55338742</v>
       </c>
       <c r="O35">
-        <v>0.166286337</v>
+        <v>0.166016226</v>
       </c>
       <c r="P35">
-        <v>0.388001453</v>
+        <v>0.387371194</v>
       </c>
       <c r="Q35">
-        <v>0.394001453</v>
+        <v>0.393371194</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2009162341351798</v>
+        <v>0.2027421744017964</v>
       </c>
       <c r="T35">
-        <v>1.081539031831604</v>
+        <v>1.094270295449169</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.65521918430167</v>
+        <v>19.07712450241045</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1457812351051856</v>
+        <v>0.1453292933398008</v>
       </c>
       <c r="C36">
-        <v>1.415937928394515</v>
+        <v>1.404855967038225</v>
       </c>
       <c r="D36">
-        <v>1.960537928394515</v>
+        <v>1.967355967038225</v>
       </c>
       <c r="E36">
-        <v>0.2586000000000001</v>
+        <v>0.2765000000000001</v>
       </c>
       <c r="F36">
-        <v>0.6086</v>
+        <v>0.6265000000000001</v>
       </c>
       <c r="G36">
         <v>0.064</v>
@@ -4239,28 +4239,28 @@
         <v>0.584</v>
       </c>
       <c r="M36">
-        <v>0.03061258</v>
+        <v>0.03151295</v>
       </c>
       <c r="N36">
-        <v>0.55338742</v>
+        <v>0.55248705</v>
       </c>
       <c r="O36">
-        <v>0.166016226</v>
+        <v>0.165746115</v>
       </c>
       <c r="P36">
-        <v>0.387371194</v>
+        <v>0.386740935</v>
       </c>
       <c r="Q36">
-        <v>0.393371194</v>
+        <v>0.392740935</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2027421744017964</v>
+        <v>0.2046242974458474</v>
       </c>
       <c r="T36">
-        <v>1.094270295449169</v>
+        <v>1.107393290254967</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>19.07712450241045</v>
+        <v>18.53206380234158</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1453292933398008</v>
+        <v>0.144877351574416</v>
       </c>
       <c r="C37">
-        <v>1.404855967038225</v>
+        <v>1.393821592494344</v>
       </c>
       <c r="D37">
-        <v>1.967355967038225</v>
+        <v>1.974221592494344</v>
       </c>
       <c r="E37">
-        <v>0.2765000000000001</v>
+        <v>0.2944000000000001</v>
       </c>
       <c r="F37">
-        <v>0.6265000000000001</v>
+        <v>0.6444000000000001</v>
       </c>
       <c r="G37">
         <v>0.064</v>
@@ -4321,28 +4321,28 @@
         <v>0.584</v>
       </c>
       <c r="M37">
-        <v>0.03151295</v>
+        <v>0.03241332</v>
       </c>
       <c r="N37">
-        <v>0.55248705</v>
+        <v>0.55158668</v>
       </c>
       <c r="O37">
-        <v>0.165746115</v>
+        <v>0.165476004</v>
       </c>
       <c r="P37">
-        <v>0.386740935</v>
+        <v>0.386110676</v>
       </c>
       <c r="Q37">
-        <v>0.392740935</v>
+        <v>0.392110676</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2046242974458474</v>
+        <v>0.206565236835025</v>
       </c>
       <c r="T37">
-        <v>1.107393290254967</v>
+        <v>1.120926378648446</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.53206380234158</v>
+        <v>18.01728425227653</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.144877351574416</v>
+        <v>0.1444254098090312</v>
       </c>
       <c r="C38">
-        <v>1.393821592494344</v>
+        <v>1.382835304709072</v>
       </c>
       <c r="D38">
-        <v>1.974221592494344</v>
+        <v>1.981135304709072</v>
       </c>
       <c r="E38">
-        <v>0.2944</v>
+        <v>0.3123</v>
       </c>
       <c r="F38">
-        <v>0.6444</v>
+        <v>0.6623</v>
       </c>
       <c r="G38">
         <v>0.064</v>
@@ -4403,28 +4403,28 @@
         <v>0.584</v>
       </c>
       <c r="M38">
-        <v>0.03241332</v>
+        <v>0.03331369</v>
       </c>
       <c r="N38">
-        <v>0.55158668</v>
+        <v>0.55068631</v>
       </c>
       <c r="O38">
-        <v>0.165476004</v>
+        <v>0.165205893</v>
       </c>
       <c r="P38">
-        <v>0.386110676</v>
+        <v>0.385480417</v>
       </c>
       <c r="Q38">
-        <v>0.392110676</v>
+        <v>0.391480417</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.206565236835025</v>
+        <v>0.2085677933476685</v>
       </c>
       <c r="T38">
-        <v>1.120926378648446</v>
+        <v>1.134889088895686</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>18.01728425227654</v>
+        <v>17.53033062383663</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1444254098090312</v>
+        <v>0.1439734680436464</v>
       </c>
       <c r="C39">
-        <v>1.382835304709072</v>
+        <v>1.37189761065645</v>
       </c>
       <c r="D39">
-        <v>1.981135304709072</v>
+        <v>1.98809761065645</v>
       </c>
       <c r="E39">
-        <v>0.3123</v>
+        <v>0.3302</v>
       </c>
       <c r="F39">
-        <v>0.6623</v>
+        <v>0.6802</v>
       </c>
       <c r="G39">
         <v>0.064</v>
@@ -4485,28 +4485,28 @@
         <v>0.584</v>
       </c>
       <c r="M39">
-        <v>0.03331369</v>
+        <v>0.03421406</v>
       </c>
       <c r="N39">
-        <v>0.55068631</v>
+        <v>0.5497859399999999</v>
       </c>
       <c r="O39">
-        <v>0.165205893</v>
+        <v>0.164935782</v>
       </c>
       <c r="P39">
-        <v>0.385480417</v>
+        <v>0.3848501579999999</v>
       </c>
       <c r="Q39">
-        <v>0.391480417</v>
+        <v>0.3908501579999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2085677933476685</v>
+        <v>0.2106349484574941</v>
       </c>
       <c r="T39">
-        <v>1.134889088895686</v>
+        <v>1.149302209150902</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.53033062383663</v>
+        <v>17.06900613373566</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1439734680436464</v>
+        <v>0.1435215262782616</v>
       </c>
       <c r="C40">
-        <v>1.37189761065645</v>
+        <v>1.361009024462293</v>
       </c>
       <c r="D40">
-        <v>1.98809761065645</v>
+        <v>1.995109024462293</v>
       </c>
       <c r="E40">
-        <v>0.3302</v>
+        <v>0.3481000000000001</v>
       </c>
       <c r="F40">
-        <v>0.6802</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="G40">
         <v>0.064</v>
@@ -4567,28 +4567,28 @@
         <v>0.584</v>
       </c>
       <c r="M40">
-        <v>0.03421406</v>
+        <v>0.03511443</v>
       </c>
       <c r="N40">
-        <v>0.5497859399999999</v>
+        <v>0.5488855699999999</v>
       </c>
       <c r="O40">
-        <v>0.164935782</v>
+        <v>0.164665671</v>
       </c>
       <c r="P40">
-        <v>0.3848501579999999</v>
+        <v>0.384219899</v>
       </c>
       <c r="Q40">
-        <v>0.3908501579999999</v>
+        <v>0.390219899</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2106349484574941</v>
+        <v>0.2127698791446911</v>
       </c>
       <c r="T40">
-        <v>1.149302209150902</v>
+        <v>1.16418789072596</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>17.06900613373566</v>
+        <v>16.63133930979372</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1435215262782616</v>
+        <v>0.1430695845128768</v>
       </c>
       <c r="C41">
-        <v>1.361009024462293</v>
+        <v>1.350170067530745</v>
       </c>
       <c r="D41">
-        <v>1.995109024462293</v>
+        <v>2.002170067530745</v>
       </c>
       <c r="E41">
-        <v>0.3481000000000001</v>
+        <v>0.3660000000000001</v>
       </c>
       <c r="F41">
-        <v>0.6981000000000001</v>
+        <v>0.7160000000000001</v>
       </c>
       <c r="G41">
         <v>0.064</v>
@@ -4649,28 +4649,28 @@
         <v>0.584</v>
       </c>
       <c r="M41">
-        <v>0.03511443</v>
+        <v>0.0360148</v>
       </c>
       <c r="N41">
-        <v>0.5488855699999999</v>
+        <v>0.5479852</v>
       </c>
       <c r="O41">
-        <v>0.164665671</v>
+        <v>0.16439556</v>
       </c>
       <c r="P41">
-        <v>0.384219899</v>
+        <v>0.38358964</v>
       </c>
       <c r="Q41">
-        <v>0.390219899</v>
+        <v>0.38958964</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2127698791446911</v>
+        <v>0.214975974188128</v>
       </c>
       <c r="T41">
-        <v>1.16418789072596</v>
+        <v>1.179569761686855</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.63133930979372</v>
+        <v>16.21555582704888</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1430695845128768</v>
+        <v>0.1426176427474919</v>
       </c>
       <c r="C42">
-        <v>1.350170067530745</v>
+        <v>1.33938126867353</v>
       </c>
       <c r="D42">
-        <v>2.002170067530745</v>
+        <v>2.009281268673531</v>
       </c>
       <c r="E42">
-        <v>0.3660000000000001</v>
+        <v>0.3839000000000001</v>
       </c>
       <c r="F42">
-        <v>0.7160000000000001</v>
+        <v>0.7339000000000001</v>
       </c>
       <c r="G42">
         <v>0.064</v>
@@ -4731,28 +4731,28 @@
         <v>0.584</v>
       </c>
       <c r="M42">
-        <v>0.0360148</v>
+        <v>0.03691517</v>
       </c>
       <c r="N42">
-        <v>0.5479852</v>
+        <v>0.54708483</v>
       </c>
       <c r="O42">
-        <v>0.16439556</v>
+        <v>0.164125449</v>
       </c>
       <c r="P42">
-        <v>0.38358964</v>
+        <v>0.382959381</v>
       </c>
       <c r="Q42">
-        <v>0.38958964</v>
+        <v>0.388959381</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.214975974188128</v>
+        <v>0.2172568521143931</v>
       </c>
       <c r="T42">
-        <v>1.179569761686855</v>
+        <v>1.195473052002355</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>16.21555582704888</v>
+        <v>15.82005446541354</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1426176427474919</v>
+        <v>0.1421657009821072</v>
       </c>
       <c r="C43">
-        <v>1.33938126867353</v>
+        <v>1.328643164241974</v>
       </c>
       <c r="D43">
-        <v>2.009281268673531</v>
+        <v>2.016443164241974</v>
       </c>
       <c r="E43">
-        <v>0.3839000000000001</v>
+        <v>0.4018000000000002</v>
       </c>
       <c r="F43">
-        <v>0.7339000000000001</v>
+        <v>0.7518000000000001</v>
       </c>
       <c r="G43">
         <v>0.064</v>
@@ -4813,28 +4813,28 @@
         <v>0.584</v>
       </c>
       <c r="M43">
-        <v>0.03691517</v>
+        <v>0.03781554</v>
       </c>
       <c r="N43">
-        <v>0.54708483</v>
+        <v>0.54618446</v>
       </c>
       <c r="O43">
-        <v>0.164125449</v>
+        <v>0.163855338</v>
       </c>
       <c r="P43">
-        <v>0.382959381</v>
+        <v>0.382329122</v>
       </c>
       <c r="Q43">
-        <v>0.388959381</v>
+        <v>0.388329122</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2172568521143931</v>
+        <v>0.219616381003633</v>
       </c>
       <c r="T43">
-        <v>1.195473052002355</v>
+        <v>1.21192473163908</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.82005446541354</v>
+        <v>15.44338650195131</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1421657009821072</v>
+        <v>0.1417137592167224</v>
       </c>
       <c r="C44">
-        <v>1.328643164241974</v>
+        <v>1.317956298261853</v>
       </c>
       <c r="D44">
-        <v>2.016443164241974</v>
+        <v>2.023656298261853</v>
       </c>
       <c r="E44">
-        <v>0.4018</v>
+        <v>0.4197000000000001</v>
       </c>
       <c r="F44">
-        <v>0.7518</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="G44">
         <v>0.064</v>
@@ -4895,28 +4895,28 @@
         <v>0.584</v>
       </c>
       <c r="M44">
-        <v>0.03781554</v>
+        <v>0.03871591</v>
       </c>
       <c r="N44">
-        <v>0.54618446</v>
+        <v>0.54528409</v>
       </c>
       <c r="O44">
-        <v>0.163855338</v>
+        <v>0.163585227</v>
       </c>
       <c r="P44">
-        <v>0.382329122</v>
+        <v>0.381698863</v>
       </c>
       <c r="Q44">
-        <v>0.388329122</v>
+        <v>0.387698863</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.219616381003633</v>
+        <v>0.2220587003802146</v>
       </c>
       <c r="T44">
-        <v>1.21192473163908</v>
+        <v>1.228953663192883</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.44338650195131</v>
+        <v>15.08423797865012</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1417137592167224</v>
+        <v>0.1412618174513375</v>
       </c>
       <c r="C45">
-        <v>1.317956298261853</v>
+        <v>1.307321222571153</v>
       </c>
       <c r="D45">
-        <v>2.023656298261853</v>
+        <v>2.030921222571152</v>
       </c>
       <c r="E45">
-        <v>0.4197000000000001</v>
+        <v>0.4376</v>
       </c>
       <c r="F45">
-        <v>0.7697000000000001</v>
+        <v>0.7876</v>
       </c>
       <c r="G45">
         <v>0.064</v>
@@ -4977,28 +4977,28 @@
         <v>0.584</v>
       </c>
       <c r="M45">
-        <v>0.03871591</v>
+        <v>0.03961628</v>
       </c>
       <c r="N45">
-        <v>0.54528409</v>
+        <v>0.54438372</v>
       </c>
       <c r="O45">
-        <v>0.163585227</v>
+        <v>0.163315116</v>
       </c>
       <c r="P45">
-        <v>0.381698863</v>
+        <v>0.381068604</v>
       </c>
       <c r="Q45">
-        <v>0.387698863</v>
+        <v>0.387068604</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2220587003802146</v>
+        <v>0.224588245448817</v>
       </c>
       <c r="T45">
-        <v>1.228953663192883</v>
+        <v>1.246590770873608</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>15.08423797865012</v>
+        <v>14.74141438822626</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1412618174513375</v>
+        <v>0.1408098756859527</v>
       </c>
       <c r="C46">
-        <v>1.307321222571153</v>
+        <v>1.2967384969608</v>
       </c>
       <c r="D46">
-        <v>2.030921222571152</v>
+        <v>2.0382384969608</v>
       </c>
       <c r="E46">
-        <v>0.4376</v>
+        <v>0.4555</v>
       </c>
       <c r="F46">
-        <v>0.7876</v>
+        <v>0.8055</v>
       </c>
       <c r="G46">
         <v>0.064</v>
@@ -5059,28 +5059,28 @@
         <v>0.584</v>
       </c>
       <c r="M46">
-        <v>0.03961628</v>
+        <v>0.04051664999999999</v>
       </c>
       <c r="N46">
-        <v>0.54438372</v>
+        <v>0.5434833499999999</v>
       </c>
       <c r="O46">
-        <v>0.163315116</v>
+        <v>0.163045005</v>
       </c>
       <c r="P46">
-        <v>0.381068604</v>
+        <v>0.380438345</v>
       </c>
       <c r="Q46">
-        <v>0.387068604</v>
+        <v>0.386438345</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.224588245448817</v>
+        <v>0.2272097739744595</v>
       </c>
       <c r="T46">
-        <v>1.246590770873608</v>
+        <v>1.26486922792454</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.74141438822626</v>
+        <v>14.41382740182123</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1408098756859527</v>
+        <v>0.1403579339205679</v>
       </c>
       <c r="C47">
-        <v>1.2967384969608</v>
+        <v>1.286208689318454</v>
       </c>
       <c r="D47">
-        <v>2.0382384969608</v>
+        <v>2.045608689318454</v>
       </c>
       <c r="E47">
-        <v>0.4555</v>
+        <v>0.4734</v>
       </c>
       <c r="F47">
-        <v>0.8055</v>
+        <v>0.8234</v>
       </c>
       <c r="G47">
         <v>0.064</v>
@@ -5141,28 +5141,28 @@
         <v>0.584</v>
       </c>
       <c r="M47">
-        <v>0.04051664999999999</v>
+        <v>0.04141702</v>
       </c>
       <c r="N47">
-        <v>0.5434833499999999</v>
+        <v>0.5425829799999999</v>
       </c>
       <c r="O47">
-        <v>0.163045005</v>
+        <v>0.162774894</v>
       </c>
       <c r="P47">
-        <v>0.380438345</v>
+        <v>0.3798080859999999</v>
       </c>
       <c r="Q47">
-        <v>0.386438345</v>
+        <v>0.3858080859999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2272097739744595</v>
+        <v>0.2299283961491998</v>
       </c>
       <c r="T47">
-        <v>1.26486922792454</v>
+        <v>1.283824664866248</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.41382740182123</v>
+        <v>14.10048332786859</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1403579339205679</v>
+        <v>0.1399059921551831</v>
       </c>
       <c r="C48">
-        <v>1.286208689318454</v>
+        <v>1.27573237577542</v>
       </c>
       <c r="D48">
-        <v>2.045608689318454</v>
+        <v>2.05303237577542</v>
       </c>
       <c r="E48">
-        <v>0.4734</v>
+        <v>0.4913000000000001</v>
       </c>
       <c r="F48">
-        <v>0.8234</v>
+        <v>0.8413</v>
       </c>
       <c r="G48">
         <v>0.064</v>
@@ -5223,28 +5223,28 @@
         <v>0.584</v>
       </c>
       <c r="M48">
-        <v>0.04141702</v>
+        <v>0.04231739</v>
       </c>
       <c r="N48">
-        <v>0.5425829799999999</v>
+        <v>0.54168261</v>
       </c>
       <c r="O48">
-        <v>0.162774894</v>
+        <v>0.162504783</v>
       </c>
       <c r="P48">
-        <v>0.3798080859999999</v>
+        <v>0.379177827</v>
       </c>
       <c r="Q48">
-        <v>0.3858080859999999</v>
+        <v>0.385177827</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2299283961491998</v>
+        <v>0.2327496078399681</v>
       </c>
       <c r="T48">
-        <v>1.283824664866248</v>
+        <v>1.30349540131519</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>14.10048332786859</v>
+        <v>13.80047304429692</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1399059921551831</v>
+        <v>0.1394540503897983</v>
       </c>
       <c r="C49">
-        <v>1.27573237577542</v>
+        <v>1.265310140856784</v>
       </c>
       <c r="D49">
-        <v>2.05303237577542</v>
+        <v>2.060510140856784</v>
       </c>
       <c r="E49">
-        <v>0.4913000000000001</v>
+        <v>0.5092000000000001</v>
       </c>
       <c r="F49">
-        <v>0.8413</v>
+        <v>0.8592000000000001</v>
       </c>
       <c r="G49">
         <v>0.064</v>
@@ -5305,28 +5305,28 @@
         <v>0.584</v>
       </c>
       <c r="M49">
-        <v>0.04231739</v>
+        <v>0.04321776</v>
       </c>
       <c r="N49">
-        <v>0.54168261</v>
+        <v>0.54078224</v>
       </c>
       <c r="O49">
-        <v>0.162504783</v>
+        <v>0.162234672</v>
       </c>
       <c r="P49">
-        <v>0.379177827</v>
+        <v>0.378547568</v>
       </c>
       <c r="Q49">
-        <v>0.385177827</v>
+        <v>0.384547568</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2327496078399681</v>
+        <v>0.2356793276726891</v>
       </c>
       <c r="T49">
-        <v>1.30349540131519</v>
+        <v>1.323922704550631</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.80047304429692</v>
+        <v>13.5129631892074</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1394540503897983</v>
+        <v>0.1390021086244135</v>
       </c>
       <c r="C50">
-        <v>1.265310140856784</v>
+        <v>1.254942577634832</v>
       </c>
       <c r="D50">
-        <v>2.060510140856784</v>
+        <v>2.068042577634832</v>
       </c>
       <c r="E50">
-        <v>0.5092</v>
+        <v>0.5271</v>
       </c>
       <c r="F50">
-        <v>0.8592</v>
+        <v>0.8771</v>
       </c>
       <c r="G50">
         <v>0.064</v>
@@ -5387,28 +5387,28 @@
         <v>0.584</v>
       </c>
       <c r="M50">
-        <v>0.04321775999999999</v>
+        <v>0.04411813</v>
       </c>
       <c r="N50">
-        <v>0.54078224</v>
+        <v>0.53988187</v>
       </c>
       <c r="O50">
-        <v>0.162234672</v>
+        <v>0.161964561</v>
       </c>
       <c r="P50">
-        <v>0.378547568</v>
+        <v>0.377917309</v>
       </c>
       <c r="Q50">
-        <v>0.384547568</v>
+        <v>0.383917309</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2356793276726891</v>
+        <v>0.2387239384792421</v>
       </c>
       <c r="T50">
-        <v>1.323922704550631</v>
+        <v>1.345151078501186</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.5129631892074</v>
+        <v>13.23718843024398</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1390021086244135</v>
+        <v>0.1385501668590287</v>
       </c>
       <c r="C51">
-        <v>1.254942577634832</v>
+        <v>1.244630287885846</v>
       </c>
       <c r="D51">
-        <v>2.068042577634832</v>
+        <v>2.075630287885846</v>
       </c>
       <c r="E51">
-        <v>0.5271</v>
+        <v>0.545</v>
       </c>
       <c r="F51">
-        <v>0.8771</v>
+        <v>0.895</v>
       </c>
       <c r="G51">
         <v>0.064</v>
@@ -5469,28 +5469,28 @@
         <v>0.584</v>
       </c>
       <c r="M51">
-        <v>0.04411813</v>
+        <v>0.0450185</v>
       </c>
       <c r="N51">
-        <v>0.53988187</v>
+        <v>0.5389815</v>
       </c>
       <c r="O51">
-        <v>0.161964561</v>
+        <v>0.16169445</v>
       </c>
       <c r="P51">
-        <v>0.377917309</v>
+        <v>0.37728705</v>
       </c>
       <c r="Q51">
-        <v>0.383917309</v>
+        <v>0.38328705</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2387239384792421</v>
+        <v>0.2418903337180574</v>
       </c>
       <c r="T51">
-        <v>1.345151078501186</v>
+        <v>1.367228587409763</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>13.23718843024398</v>
+        <v>12.97244466163911</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1385501668590287</v>
+        <v>0.1386337250936439</v>
       </c>
       <c r="C52">
-        <v>1.244630287885846</v>
+        <v>1.225323224917804</v>
       </c>
       <c r="D52">
-        <v>2.075630287885846</v>
+        <v>2.074223224917804</v>
       </c>
       <c r="E52">
-        <v>0.545</v>
+        <v>0.5629000000000001</v>
       </c>
       <c r="F52">
-        <v>0.895</v>
+        <v>0.9129</v>
       </c>
       <c r="G52">
         <v>0.064</v>
@@ -5551,45 +5551,45 @@
         <v>0.584</v>
       </c>
       <c r="M52">
-        <v>0.0450185</v>
+        <v>0.04728822</v>
       </c>
       <c r="N52">
-        <v>0.5389815</v>
+        <v>0.53671178</v>
       </c>
       <c r="O52">
-        <v>0.16169445</v>
+        <v>0.161013534</v>
       </c>
       <c r="P52">
-        <v>0.37728705</v>
+        <v>0.375698246</v>
       </c>
       <c r="Q52">
-        <v>0.38328705</v>
+        <v>0.381698246</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2418903337180574</v>
+        <v>0.2451859695788651</v>
       </c>
       <c r="T52">
-        <v>1.367228587409763</v>
+        <v>1.390207219130936</v>
       </c>
       <c r="U52">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y52">
-        <v>12.97244466163911</v>
+        <v>12.34979874480367</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1386337250936439</v>
+        <v>0.1381922833282591</v>
       </c>
       <c r="C53">
-        <v>1.225323224917804</v>
+        <v>1.214878460068014</v>
       </c>
       <c r="D53">
-        <v>2.074223224917804</v>
+        <v>2.081678460068014</v>
       </c>
       <c r="E53">
-        <v>0.5629000000000001</v>
+        <v>0.5808000000000001</v>
       </c>
       <c r="F53">
-        <v>0.9129</v>
+        <v>0.9308000000000001</v>
       </c>
       <c r="G53">
         <v>0.064</v>
@@ -5633,28 +5633,28 @@
         <v>0.584</v>
       </c>
       <c r="M53">
-        <v>0.04728822</v>
+        <v>0.04821544000000001</v>
       </c>
       <c r="N53">
-        <v>0.53671178</v>
+        <v>0.53578456</v>
       </c>
       <c r="O53">
-        <v>0.161013534</v>
+        <v>0.160735368</v>
       </c>
       <c r="P53">
-        <v>0.375698246</v>
+        <v>0.375049192</v>
       </c>
       <c r="Q53">
-        <v>0.381698246</v>
+        <v>0.381049192</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2451859695788651</v>
+        <v>0.2486189236005397</v>
       </c>
       <c r="T53">
-        <v>1.390207219130936</v>
+        <v>1.414143293840491</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.34979874480367</v>
+        <v>12.11230261509591</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1381922833282591</v>
+        <v>0.1377508415628743</v>
       </c>
       <c r="C54">
-        <v>1.214878460068014</v>
+        <v>1.204487480192077</v>
       </c>
       <c r="D54">
-        <v>2.081678460068014</v>
+        <v>2.089187480192077</v>
       </c>
       <c r="E54">
-        <v>0.5808000000000001</v>
+        <v>0.5987000000000001</v>
       </c>
       <c r="F54">
-        <v>0.9308000000000001</v>
+        <v>0.9487000000000001</v>
       </c>
       <c r="G54">
         <v>0.064</v>
@@ -5715,28 +5715,28 @@
         <v>0.584</v>
       </c>
       <c r="M54">
-        <v>0.04821544000000001</v>
+        <v>0.04914266</v>
       </c>
       <c r="N54">
-        <v>0.53578456</v>
+        <v>0.53485734</v>
       </c>
       <c r="O54">
-        <v>0.160735368</v>
+        <v>0.160457202</v>
       </c>
       <c r="P54">
-        <v>0.375049192</v>
+        <v>0.3744001379999999</v>
       </c>
       <c r="Q54">
-        <v>0.381049192</v>
+        <v>0.3804001379999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2486189236005397</v>
+        <v>0.2521979607720729</v>
       </c>
       <c r="T54">
-        <v>1.414143293840491</v>
+        <v>1.439097924920665</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>12.11230261509591</v>
+        <v>11.88376860349033</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1377508415628743</v>
+        <v>0.1373093997974895</v>
       </c>
       <c r="C55">
-        <v>1.204487480192077</v>
+        <v>1.194150869435786</v>
       </c>
       <c r="D55">
-        <v>2.089187480192077</v>
+        <v>2.096750869435786</v>
       </c>
       <c r="E55">
-        <v>0.5987000000000001</v>
+        <v>0.6166000000000001</v>
       </c>
       <c r="F55">
-        <v>0.9487000000000001</v>
+        <v>0.9666000000000001</v>
       </c>
       <c r="G55">
         <v>0.064</v>
@@ -5797,28 +5797,28 @@
         <v>0.584</v>
       </c>
       <c r="M55">
-        <v>0.04914266</v>
+        <v>0.05006988</v>
       </c>
       <c r="N55">
-        <v>0.53485734</v>
+        <v>0.53393012</v>
       </c>
       <c r="O55">
-        <v>0.160457202</v>
+        <v>0.160179036</v>
       </c>
       <c r="P55">
-        <v>0.3744001379999999</v>
+        <v>0.373751084</v>
       </c>
       <c r="Q55">
-        <v>0.3804001379999999</v>
+        <v>0.379751084</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2521979607720729</v>
+        <v>0.2559326082554119</v>
       </c>
       <c r="T55">
-        <v>1.439097924920665</v>
+        <v>1.465137539960846</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.88376860349033</v>
+        <v>11.6636988145368</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1373093997974895</v>
+        <v>0.1368679580321046</v>
       </c>
       <c r="C56">
-        <v>1.194150869435786</v>
+        <v>1.183869220434695</v>
       </c>
       <c r="D56">
-        <v>2.096750869435786</v>
+        <v>2.104369220434695</v>
       </c>
       <c r="E56">
-        <v>0.6166000000000001</v>
+        <v>0.6345000000000002</v>
       </c>
       <c r="F56">
-        <v>0.9666000000000001</v>
+        <v>0.9845000000000002</v>
       </c>
       <c r="G56">
         <v>0.064</v>
@@ -5879,28 +5879,28 @@
         <v>0.584</v>
       </c>
       <c r="M56">
-        <v>0.05006988</v>
+        <v>0.0509971</v>
       </c>
       <c r="N56">
-        <v>0.53393012</v>
+        <v>0.5330028999999999</v>
       </c>
       <c r="O56">
-        <v>0.160179036</v>
+        <v>0.15990087</v>
       </c>
       <c r="P56">
-        <v>0.373751084</v>
+        <v>0.37310203</v>
       </c>
       <c r="Q56">
-        <v>0.379751084</v>
+        <v>0.37910203</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2559326082554119</v>
+        <v>0.2598332400713437</v>
       </c>
       <c r="T56">
-        <v>1.465137539960846</v>
+        <v>1.492334471225036</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.6636988145368</v>
+        <v>11.4516315633634</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1368679580321046</v>
+        <v>0.1364265162667198</v>
       </c>
       <c r="C57">
-        <v>1.183869220434695</v>
+        <v>1.173643134468911</v>
       </c>
       <c r="D57">
-        <v>2.104369220434695</v>
+        <v>2.112043134468911</v>
       </c>
       <c r="E57">
-        <v>0.6345000000000002</v>
+        <v>0.6524000000000002</v>
       </c>
       <c r="F57">
-        <v>0.9845000000000002</v>
+        <v>1.0024</v>
       </c>
       <c r="G57">
         <v>0.064</v>
@@ -5961,28 +5961,28 @@
         <v>0.584</v>
       </c>
       <c r="M57">
-        <v>0.0509971</v>
+        <v>0.05192432000000001</v>
       </c>
       <c r="N57">
-        <v>0.5330028999999999</v>
+        <v>0.5320756799999999</v>
       </c>
       <c r="O57">
-        <v>0.15990087</v>
+        <v>0.159622704</v>
       </c>
       <c r="P57">
-        <v>0.37310203</v>
+        <v>0.3724529759999999</v>
       </c>
       <c r="Q57">
-        <v>0.37910203</v>
+        <v>0.3784529759999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2598332400713437</v>
+        <v>0.2639111733334542</v>
       </c>
       <c r="T57">
-        <v>1.492334471225036</v>
+        <v>1.520767626637598</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.4516315633634</v>
+        <v>11.24713814258906</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1364265162667198</v>
+        <v>0.135985074501335</v>
       </c>
       <c r="C58">
-        <v>1.173643134468911</v>
+        <v>1.163473221621297</v>
       </c>
       <c r="D58">
-        <v>2.112043134468911</v>
+        <v>2.119773221621297</v>
       </c>
       <c r="E58">
-        <v>0.6524000000000002</v>
+        <v>0.6703000000000002</v>
       </c>
       <c r="F58">
-        <v>1.0024</v>
+        <v>1.0203</v>
       </c>
       <c r="G58">
         <v>0.064</v>
@@ -6043,28 +6043,28 @@
         <v>0.584</v>
       </c>
       <c r="M58">
-        <v>0.05192432000000001</v>
+        <v>0.05285154000000001</v>
       </c>
       <c r="N58">
-        <v>0.5320756799999999</v>
+        <v>0.5311484599999999</v>
       </c>
       <c r="O58">
-        <v>0.159622704</v>
+        <v>0.159344538</v>
       </c>
       <c r="P58">
-        <v>0.3724529759999999</v>
+        <v>0.371803922</v>
       </c>
       <c r="Q58">
-        <v>0.3784529759999999</v>
+        <v>0.377803922</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2639111733334542</v>
+        <v>0.2681787779100815</v>
       </c>
       <c r="T58">
-        <v>1.520767626637598</v>
+        <v>1.55052325439493</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.24713814258906</v>
+        <v>11.04981992956118</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.135985074501335</v>
+        <v>0.1355436327359502</v>
       </c>
       <c r="C59">
-        <v>1.163473221621297</v>
+        <v>1.153360100939143</v>
       </c>
       <c r="D59">
-        <v>2.119773221621297</v>
+        <v>2.127560100939143</v>
       </c>
       <c r="E59">
-        <v>0.6703000000000002</v>
+        <v>0.6882000000000003</v>
       </c>
       <c r="F59">
-        <v>1.0203</v>
+        <v>1.0382</v>
       </c>
       <c r="G59">
         <v>0.064</v>
@@ -6125,28 +6125,28 @@
         <v>0.584</v>
       </c>
       <c r="M59">
-        <v>0.05285154000000001</v>
+        <v>0.05377876000000001</v>
       </c>
       <c r="N59">
-        <v>0.5311484599999999</v>
+        <v>0.5302212399999999</v>
       </c>
       <c r="O59">
-        <v>0.159344538</v>
+        <v>0.159066372</v>
       </c>
       <c r="P59">
-        <v>0.371803922</v>
+        <v>0.371154868</v>
       </c>
       <c r="Q59">
-        <v>0.377803922</v>
+        <v>0.377154868</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2681787779100815</v>
+        <v>0.2726496017522625</v>
       </c>
       <c r="T59">
-        <v>1.55052325439493</v>
+        <v>1.581695816807373</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>11.04981992956118</v>
+        <v>10.85930579284461</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1355436327359502</v>
+        <v>0.1351021909705654</v>
       </c>
       <c r="C60">
-        <v>1.153360100939143</v>
+        <v>1.143304400599439</v>
       </c>
       <c r="D60">
-        <v>2.127560100939143</v>
+        <v>2.135404400599439</v>
       </c>
       <c r="E60">
-        <v>0.6882</v>
+        <v>0.7061000000000001</v>
       </c>
       <c r="F60">
-        <v>1.0382</v>
+        <v>1.0561</v>
       </c>
       <c r="G60">
         <v>0.064</v>
@@ -6207,28 +6207,28 @@
         <v>0.584</v>
       </c>
       <c r="M60">
-        <v>0.05377876</v>
+        <v>0.05470598</v>
       </c>
       <c r="N60">
-        <v>0.5302212399999999</v>
+        <v>0.5292940199999999</v>
       </c>
       <c r="O60">
-        <v>0.159066372</v>
+        <v>0.158788206</v>
       </c>
       <c r="P60">
-        <v>0.371154868</v>
+        <v>0.3705058139999999</v>
       </c>
       <c r="Q60">
-        <v>0.377154868</v>
+        <v>0.3765058139999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2726496017522624</v>
+        <v>0.2773385145623546</v>
       </c>
       <c r="T60">
-        <v>1.581695816807373</v>
+        <v>1.614388992020423</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.85930579284461</v>
+        <v>10.67524976245741</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1351021909705654</v>
+        <v>0.1346607492051806</v>
       </c>
       <c r="C61">
-        <v>1.143304400599439</v>
+        <v>1.13330675807779</v>
       </c>
       <c r="D61">
-        <v>2.135404400599439</v>
+        <v>2.14330675807779</v>
       </c>
       <c r="E61">
-        <v>0.7061000000000001</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="F61">
-        <v>1.0561</v>
+        <v>1.074</v>
       </c>
       <c r="G61">
         <v>0.064</v>
@@ -6289,28 +6289,28 @@
         <v>0.584</v>
       </c>
       <c r="M61">
-        <v>0.05470598</v>
+        <v>0.0556332</v>
       </c>
       <c r="N61">
-        <v>0.5292940199999999</v>
+        <v>0.5283667999999999</v>
       </c>
       <c r="O61">
-        <v>0.158788206</v>
+        <v>0.15851004</v>
       </c>
       <c r="P61">
-        <v>0.3705058139999999</v>
+        <v>0.36985676</v>
       </c>
       <c r="Q61">
-        <v>0.3765058139999999</v>
+        <v>0.37585676</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2773385145623546</v>
+        <v>0.2822618730129515</v>
       </c>
       <c r="T61">
-        <v>1.614388992020423</v>
+        <v>1.648716825994126</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.67524976245741</v>
+        <v>10.49732893308312</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1346607492051806</v>
+        <v>0.1342193074397958</v>
       </c>
       <c r="C62">
-        <v>1.13330675807779</v>
+        <v>1.123367820321119</v>
       </c>
       <c r="D62">
-        <v>2.14330675807779</v>
+        <v>2.151267820321119</v>
       </c>
       <c r="E62">
-        <v>0.7240000000000001</v>
+        <v>0.7419000000000001</v>
       </c>
       <c r="F62">
-        <v>1.074</v>
+        <v>1.0919</v>
       </c>
       <c r="G62">
         <v>0.064</v>
@@ -6371,28 +6371,28 @@
         <v>0.584</v>
       </c>
       <c r="M62">
-        <v>0.0556332</v>
+        <v>0.05656042</v>
       </c>
       <c r="N62">
-        <v>0.5283667999999999</v>
+        <v>0.52743958</v>
       </c>
       <c r="O62">
-        <v>0.15851004</v>
+        <v>0.158231874</v>
       </c>
       <c r="P62">
-        <v>0.36985676</v>
+        <v>0.369207706</v>
       </c>
       <c r="Q62">
-        <v>0.37585676</v>
+        <v>0.375207706</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2822618730129515</v>
+        <v>0.2874377113840918</v>
       </c>
       <c r="T62">
-        <v>1.648716825994126</v>
+        <v>1.68480506171007</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.49732893308312</v>
+        <v>10.32524157352438</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1342193074397958</v>
+        <v>0.133777865674411</v>
       </c>
       <c r="C63">
-        <v>1.123367820321119</v>
+        <v>1.113488243924218</v>
       </c>
       <c r="D63">
-        <v>2.151267820321119</v>
+        <v>2.159288243924218</v>
       </c>
       <c r="E63">
-        <v>0.7419000000000001</v>
+        <v>0.7598000000000001</v>
       </c>
       <c r="F63">
-        <v>1.0919</v>
+        <v>1.1098</v>
       </c>
       <c r="G63">
         <v>0.064</v>
@@ -6453,28 +6453,28 @@
         <v>0.584</v>
       </c>
       <c r="M63">
-        <v>0.05656042</v>
+        <v>0.05748764000000001</v>
       </c>
       <c r="N63">
-        <v>0.52743958</v>
+        <v>0.5265123599999999</v>
       </c>
       <c r="O63">
-        <v>0.158231874</v>
+        <v>0.157953708</v>
       </c>
       <c r="P63">
-        <v>0.369207706</v>
+        <v>0.3685586519999999</v>
       </c>
       <c r="Q63">
-        <v>0.375207706</v>
+        <v>0.3745586519999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2874377113840918</v>
+        <v>0.2928859623010815</v>
       </c>
       <c r="T63">
-        <v>1.68480506171007</v>
+        <v>1.722792678253169</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.32524157352438</v>
+        <v>10.1587054191127</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.133777865674411</v>
+        <v>0.1333364239090262</v>
       </c>
       <c r="C64">
-        <v>1.113488243924218</v>
+        <v>1.103668695310271</v>
       </c>
       <c r="D64">
-        <v>2.159288243924218</v>
+        <v>2.16736869531027</v>
       </c>
       <c r="E64">
-        <v>0.7598000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="F64">
-        <v>1.1098</v>
+        <v>1.1277</v>
       </c>
       <c r="G64">
         <v>0.064</v>
@@ -6535,28 +6535,28 @@
         <v>0.584</v>
       </c>
       <c r="M64">
-        <v>0.05748764000000001</v>
+        <v>0.05841485999999999</v>
       </c>
       <c r="N64">
-        <v>0.5265123599999999</v>
+        <v>0.52558514</v>
       </c>
       <c r="O64">
-        <v>0.157953708</v>
+        <v>0.157675542</v>
       </c>
       <c r="P64">
-        <v>0.3685586519999999</v>
+        <v>0.367909598</v>
       </c>
       <c r="Q64">
-        <v>0.3745586519999999</v>
+        <v>0.373909598</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2928859623010815</v>
+        <v>0.2986287132676384</v>
       </c>
       <c r="T64">
-        <v>1.722792678253169</v>
+        <v>1.762833679474274</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>10.1587054191127</v>
+        <v>9.997456126745833</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1333364239090262</v>
+        <v>0.1328949821436414</v>
       </c>
       <c r="C65">
-        <v>1.103668695310271</v>
+        <v>1.093909850915441</v>
       </c>
       <c r="D65">
-        <v>2.16736869531027</v>
+        <v>2.175509850915441</v>
       </c>
       <c r="E65">
-        <v>0.7776999999999999</v>
+        <v>0.7956</v>
       </c>
       <c r="F65">
-        <v>1.1277</v>
+        <v>1.1456</v>
       </c>
       <c r="G65">
         <v>0.064</v>
@@ -6617,28 +6617,28 @@
         <v>0.584</v>
       </c>
       <c r="M65">
-        <v>0.05841485999999999</v>
+        <v>0.05934208</v>
       </c>
       <c r="N65">
-        <v>0.52558514</v>
+        <v>0.52465792</v>
       </c>
       <c r="O65">
-        <v>0.157675542</v>
+        <v>0.157397376</v>
       </c>
       <c r="P65">
-        <v>0.367909598</v>
+        <v>0.367260544</v>
       </c>
       <c r="Q65">
-        <v>0.373909598</v>
+        <v>0.373260544</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2986287132676384</v>
+        <v>0.3046905059545594</v>
       </c>
       <c r="T65">
-        <v>1.762833679474274</v>
+        <v>1.805099180763217</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.997456126745833</v>
+        <v>9.841245874765429</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1328949821436414</v>
+        <v>0.1332270403782566</v>
       </c>
       <c r="C66">
-        <v>1.093909850915441</v>
+        <v>1.069880284106925</v>
       </c>
       <c r="D66">
-        <v>2.175509850915441</v>
+        <v>2.169380284106925</v>
       </c>
       <c r="E66">
-        <v>0.7956</v>
+        <v>0.8135</v>
       </c>
       <c r="F66">
-        <v>1.1456</v>
+        <v>1.1635</v>
       </c>
       <c r="G66">
         <v>0.064</v>
@@ -6699,45 +6699,45 @@
         <v>0.584</v>
       </c>
       <c r="M66">
-        <v>0.05934208</v>
+        <v>0.06224725</v>
       </c>
       <c r="N66">
-        <v>0.52465792</v>
+        <v>0.52175275</v>
       </c>
       <c r="O66">
-        <v>0.157397376</v>
+        <v>0.156525825</v>
       </c>
       <c r="P66">
-        <v>0.367260544</v>
+        <v>0.365226925</v>
       </c>
       <c r="Q66">
-        <v>0.373260544</v>
+        <v>0.371226925</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3046905059545594</v>
+        <v>0.3110986867950188</v>
       </c>
       <c r="T66">
-        <v>1.805099180763217</v>
+        <v>1.849779853554386</v>
       </c>
       <c r="U66">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>9.841245874765429</v>
+        <v>9.381940567655599</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1332270403782566</v>
+        <v>0.1327974986128718</v>
       </c>
       <c r="C67">
-        <v>1.069880284106925</v>
+        <v>1.059915912422576</v>
       </c>
       <c r="D67">
-        <v>2.169380284106925</v>
+        <v>2.177315912422576</v>
       </c>
       <c r="E67">
-        <v>0.8135</v>
+        <v>0.8314</v>
       </c>
       <c r="F67">
-        <v>1.1635</v>
+        <v>1.1814</v>
       </c>
       <c r="G67">
         <v>0.064</v>
@@ -6781,28 +6781,28 @@
         <v>0.584</v>
       </c>
       <c r="M67">
-        <v>0.06224725</v>
+        <v>0.06320489999999999</v>
       </c>
       <c r="N67">
-        <v>0.52175275</v>
+        <v>0.5207951</v>
       </c>
       <c r="O67">
-        <v>0.156525825</v>
+        <v>0.15623853</v>
       </c>
       <c r="P67">
-        <v>0.365226925</v>
+        <v>0.36455657</v>
       </c>
       <c r="Q67">
-        <v>0.371226925</v>
+        <v>0.37055657</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3110986867950188</v>
+        <v>0.3178838194496229</v>
       </c>
       <c r="T67">
-        <v>1.849779853554386</v>
+        <v>1.897088801215623</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.381940567655599</v>
+        <v>9.239789952994151</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1327974986128718</v>
+        <v>0.132367956847487</v>
       </c>
       <c r="C68">
-        <v>1.059915912422576</v>
+        <v>1.050009811207097</v>
       </c>
       <c r="D68">
-        <v>2.177315912422576</v>
+        <v>2.185309811207097</v>
       </c>
       <c r="E68">
-        <v>0.8314</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F68">
-        <v>1.1814</v>
+        <v>1.1993</v>
       </c>
       <c r="G68">
         <v>0.064</v>
@@ -6863,28 +6863,28 @@
         <v>0.584</v>
       </c>
       <c r="M68">
-        <v>0.06320489999999999</v>
+        <v>0.06416255</v>
       </c>
       <c r="N68">
-        <v>0.5207951</v>
+        <v>0.5198374499999999</v>
       </c>
       <c r="O68">
-        <v>0.15623853</v>
+        <v>0.155951235</v>
       </c>
       <c r="P68">
-        <v>0.36455657</v>
+        <v>0.363886215</v>
       </c>
       <c r="Q68">
-        <v>0.37055657</v>
+        <v>0.369886215</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3178838194496229</v>
+        <v>0.325080172265112</v>
       </c>
       <c r="T68">
-        <v>1.897088801215623</v>
+        <v>1.947264957826027</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.239789952994151</v>
+        <v>9.101882640262893</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.132367956847487</v>
+        <v>0.1319384150821021</v>
       </c>
       <c r="C69">
-        <v>1.050009811207097</v>
+        <v>1.040162624636263</v>
       </c>
       <c r="D69">
-        <v>2.185309811207097</v>
+        <v>2.193362624636263</v>
       </c>
       <c r="E69">
-        <v>0.8493000000000001</v>
+        <v>0.8672000000000001</v>
       </c>
       <c r="F69">
-        <v>1.1993</v>
+        <v>1.2172</v>
       </c>
       <c r="G69">
         <v>0.064</v>
@@ -6945,28 +6945,28 @@
         <v>0.584</v>
       </c>
       <c r="M69">
-        <v>0.06416255</v>
+        <v>0.0651202</v>
       </c>
       <c r="N69">
-        <v>0.5198374499999999</v>
+        <v>0.5188798</v>
       </c>
       <c r="O69">
-        <v>0.155951235</v>
+        <v>0.15566394</v>
       </c>
       <c r="P69">
-        <v>0.363886215</v>
+        <v>0.36321586</v>
       </c>
       <c r="Q69">
-        <v>0.369886215</v>
+        <v>0.36921586</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.325080172265112</v>
+        <v>0.3327262971315693</v>
       </c>
       <c r="T69">
-        <v>1.947264957826027</v>
+        <v>2.00057712422458</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>9.101882640262893</v>
+        <v>8.968031424964911</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1319384150821021</v>
+        <v>0.1315088733167174</v>
       </c>
       <c r="C70">
-        <v>1.040162624636263</v>
+        <v>1.030375006416056</v>
       </c>
       <c r="D70">
-        <v>2.193362624636263</v>
+        <v>2.201475006416056</v>
       </c>
       <c r="E70">
-        <v>0.8672000000000001</v>
+        <v>0.8851000000000001</v>
       </c>
       <c r="F70">
-        <v>1.2172</v>
+        <v>1.2351</v>
       </c>
       <c r="G70">
         <v>0.064</v>
@@ -7027,28 +7027,28 @@
         <v>0.584</v>
       </c>
       <c r="M70">
-        <v>0.0651202</v>
+        <v>0.06607785000000001</v>
       </c>
       <c r="N70">
-        <v>0.5188798</v>
+        <v>0.51792215</v>
       </c>
       <c r="O70">
-        <v>0.15566394</v>
+        <v>0.155376645</v>
       </c>
       <c r="P70">
-        <v>0.36321586</v>
+        <v>0.362545505</v>
       </c>
       <c r="Q70">
-        <v>0.36921586</v>
+        <v>0.368545505</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3327262971315693</v>
+        <v>0.3408657203765077</v>
       </c>
       <c r="T70">
-        <v>2.00057712422458</v>
+        <v>2.057328785229493</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.968031424964911</v>
+        <v>8.838059955037881</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1315088733167174</v>
+        <v>0.1310793315513326</v>
       </c>
       <c r="C71">
-        <v>1.030375006416056</v>
+        <v>1.020647619959563</v>
       </c>
       <c r="D71">
-        <v>2.201475006416056</v>
+        <v>2.209647619959563</v>
       </c>
       <c r="E71">
-        <v>0.8851000000000001</v>
+        <v>0.9030000000000001</v>
       </c>
       <c r="F71">
-        <v>1.2351</v>
+        <v>1.253</v>
       </c>
       <c r="G71">
         <v>0.064</v>
@@ -7109,28 +7109,28 @@
         <v>0.584</v>
       </c>
       <c r="M71">
-        <v>0.06607785000000001</v>
+        <v>0.0670355</v>
       </c>
       <c r="N71">
-        <v>0.51792215</v>
+        <v>0.5169644999999999</v>
       </c>
       <c r="O71">
-        <v>0.155376645</v>
+        <v>0.15508935</v>
       </c>
       <c r="P71">
-        <v>0.362545505</v>
+        <v>0.3618751499999999</v>
       </c>
       <c r="Q71">
-        <v>0.368545505</v>
+        <v>0.3678751499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3408657203765077</v>
+        <v>0.3495477718377752</v>
       </c>
       <c r="T71">
-        <v>2.057328785229493</v>
+        <v>2.117863890301399</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.838059955037881</v>
+        <v>8.711801955680198</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1310793315513326</v>
+        <v>0.1306497897859477</v>
       </c>
       <c r="C72">
-        <v>1.020647619959563</v>
+        <v>1.010981138567824</v>
       </c>
       <c r="D72">
-        <v>2.209647619959563</v>
+        <v>2.217881138567824</v>
       </c>
       <c r="E72">
-        <v>0.9030000000000001</v>
+        <v>0.9209000000000002</v>
       </c>
       <c r="F72">
-        <v>1.253</v>
+        <v>1.2709</v>
       </c>
       <c r="G72">
         <v>0.064</v>
@@ -7191,28 +7191,28 @@
         <v>0.584</v>
       </c>
       <c r="M72">
-        <v>0.0670355</v>
+        <v>0.06799315</v>
       </c>
       <c r="N72">
-        <v>0.5169644999999999</v>
+        <v>0.5160068499999999</v>
       </c>
       <c r="O72">
-        <v>0.15508935</v>
+        <v>0.154802055</v>
       </c>
       <c r="P72">
-        <v>0.3618751499999999</v>
+        <v>0.3612047949999999</v>
       </c>
       <c r="Q72">
-        <v>0.3678751499999999</v>
+        <v>0.3672047949999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3495477718377752</v>
+        <v>0.3588285854687854</v>
       </c>
       <c r="T72">
-        <v>2.117863890301399</v>
+        <v>2.18257383020585</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.711801955680198</v>
+        <v>8.589100519684703</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1306497897859477</v>
+        <v>0.1302202480205629</v>
       </c>
       <c r="C73">
-        <v>1.010981138567824</v>
+        <v>1.001376245614745</v>
       </c>
       <c r="D73">
-        <v>2.217881138567824</v>
+        <v>2.226176245614745</v>
       </c>
       <c r="E73">
-        <v>0.9208999999999999</v>
+        <v>0.9388</v>
       </c>
       <c r="F73">
-        <v>1.2709</v>
+        <v>1.2888</v>
       </c>
       <c r="G73">
         <v>0.064</v>
@@ -7273,28 +7273,28 @@
         <v>0.584</v>
       </c>
       <c r="M73">
-        <v>0.06799314999999999</v>
+        <v>0.06895079999999999</v>
       </c>
       <c r="N73">
-        <v>0.51600685</v>
+        <v>0.5150492</v>
       </c>
       <c r="O73">
-        <v>0.154802055</v>
+        <v>0.15451476</v>
       </c>
       <c r="P73">
-        <v>0.361204795</v>
+        <v>0.36053444</v>
       </c>
       <c r="Q73">
-        <v>0.367204795</v>
+        <v>0.36653444</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3588285854687853</v>
+        <v>0.3687723143591533</v>
       </c>
       <c r="T73">
-        <v>2.182573830205849</v>
+        <v>2.251905908674904</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.589100519684706</v>
+        <v>8.469807456911305</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1302202480205629</v>
+        <v>0.1297907062551781</v>
       </c>
       <c r="C74">
-        <v>1.001376245614745</v>
+        <v>0.9918336347361698</v>
       </c>
       <c r="D74">
-        <v>2.226176245614745</v>
+        <v>2.23453363473617</v>
       </c>
       <c r="E74">
-        <v>0.9388</v>
+        <v>0.9567</v>
       </c>
       <c r="F74">
-        <v>1.2888</v>
+        <v>1.3067</v>
       </c>
       <c r="G74">
         <v>0.064</v>
@@ -7355,28 +7355,28 @@
         <v>0.584</v>
       </c>
       <c r="M74">
-        <v>0.06895079999999999</v>
+        <v>0.06990845</v>
       </c>
       <c r="N74">
-        <v>0.5150492</v>
+        <v>0.51409155</v>
       </c>
       <c r="O74">
-        <v>0.15451476</v>
+        <v>0.154227465</v>
       </c>
       <c r="P74">
-        <v>0.36053444</v>
+        <v>0.359864085</v>
       </c>
       <c r="Q74">
-        <v>0.36653444</v>
+        <v>0.365864085</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3687723143591533</v>
+        <v>0.379452615759919</v>
       </c>
       <c r="T74">
-        <v>2.251905908674904</v>
+        <v>2.326373696660185</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.469807456911305</v>
+        <v>8.353782697227588</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1297907062551781</v>
+        <v>0.1293611644897933</v>
       </c>
       <c r="C75">
-        <v>0.9918336347361698</v>
+        <v>0.982354010023234</v>
       </c>
       <c r="D75">
-        <v>2.23453363473617</v>
+        <v>2.242954010023234</v>
       </c>
       <c r="E75">
-        <v>0.9567</v>
+        <v>0.9746</v>
       </c>
       <c r="F75">
-        <v>1.3067</v>
+        <v>1.3246</v>
       </c>
       <c r="G75">
         <v>0.064</v>
@@ -7437,28 +7437,28 @@
         <v>0.584</v>
       </c>
       <c r="M75">
-        <v>0.06990845</v>
+        <v>0.0708661</v>
       </c>
       <c r="N75">
-        <v>0.51409155</v>
+        <v>0.5131338999999999</v>
       </c>
       <c r="O75">
-        <v>0.154227465</v>
+        <v>0.15394017</v>
       </c>
       <c r="P75">
-        <v>0.359864085</v>
+        <v>0.35919373</v>
       </c>
       <c r="Q75">
-        <v>0.365864085</v>
+        <v>0.36519373</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.379452615759919</v>
+        <v>0.3909544788068974</v>
       </c>
       <c r="T75">
-        <v>2.326373696660185</v>
+        <v>2.40656977602895</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.353782697227588</v>
+        <v>8.240893741859647</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1293611644897933</v>
+        <v>0.1289316227244085</v>
       </c>
       <c r="C76">
-        <v>0.982354010023234</v>
+        <v>0.9729380862201011</v>
       </c>
       <c r="D76">
-        <v>2.242954010023234</v>
+        <v>2.251438086220101</v>
       </c>
       <c r="E76">
-        <v>0.9746</v>
+        <v>0.9925</v>
       </c>
       <c r="F76">
-        <v>1.3246</v>
+        <v>1.3425</v>
       </c>
       <c r="G76">
         <v>0.064</v>
@@ -7519,28 +7519,28 @@
         <v>0.584</v>
       </c>
       <c r="M76">
-        <v>0.0708661</v>
+        <v>0.07182375000000001</v>
       </c>
       <c r="N76">
-        <v>0.5131338999999999</v>
+        <v>0.51217625</v>
       </c>
       <c r="O76">
-        <v>0.15394017</v>
+        <v>0.153652875</v>
       </c>
       <c r="P76">
-        <v>0.35919373</v>
+        <v>0.358523375</v>
       </c>
       <c r="Q76">
-        <v>0.36519373</v>
+        <v>0.364523375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3909544788068974</v>
+        <v>0.4033764908976341</v>
       </c>
       <c r="T76">
-        <v>2.40656977602895</v>
+        <v>2.493181541747215</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.240893741859647</v>
+        <v>8.131015158634852</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1289316227244085</v>
+        <v>0.1285020809590237</v>
       </c>
       <c r="C77">
-        <v>0.9729380862201011</v>
+        <v>0.9635865889262034</v>
       </c>
       <c r="D77">
-        <v>2.251438086220101</v>
+        <v>2.259986588926203</v>
       </c>
       <c r="E77">
-        <v>0.9925</v>
+        <v>1.0104</v>
       </c>
       <c r="F77">
-        <v>1.3425</v>
+        <v>1.3604</v>
       </c>
       <c r="G77">
         <v>0.064</v>
@@ -7601,28 +7601,28 @@
         <v>0.584</v>
       </c>
       <c r="M77">
-        <v>0.07182375000000001</v>
+        <v>0.0727814</v>
       </c>
       <c r="N77">
-        <v>0.51217625</v>
+        <v>0.5112186</v>
       </c>
       <c r="O77">
-        <v>0.153652875</v>
+        <v>0.15336558</v>
       </c>
       <c r="P77">
-        <v>0.358523375</v>
+        <v>0.35785302</v>
       </c>
       <c r="Q77">
-        <v>0.364523375</v>
+        <v>0.36385302</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4033764908976341</v>
+        <v>0.4168336706625988</v>
       </c>
       <c r="T77">
-        <v>2.493181541747215</v>
+        <v>2.58701095460867</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>8.131015158634852</v>
+        <v>8.024028117073868</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1285020809590237</v>
+        <v>0.1280725391936389</v>
       </c>
       <c r="C78">
-        <v>0.9635865889262034</v>
+        <v>0.9543002548031134</v>
       </c>
       <c r="D78">
-        <v>2.259986588926203</v>
+        <v>2.268600254803113</v>
       </c>
       <c r="E78">
-        <v>1.0104</v>
+        <v>1.0283</v>
       </c>
       <c r="F78">
-        <v>1.3604</v>
+        <v>1.3783</v>
       </c>
       <c r="G78">
         <v>0.064</v>
@@ -7683,28 +7683,28 @@
         <v>0.584</v>
       </c>
       <c r="M78">
-        <v>0.0727814</v>
+        <v>0.07373905</v>
       </c>
       <c r="N78">
-        <v>0.5112186</v>
+        <v>0.5102609499999999</v>
       </c>
       <c r="O78">
-        <v>0.15336558</v>
+        <v>0.153078285</v>
       </c>
       <c r="P78">
-        <v>0.35785302</v>
+        <v>0.357182665</v>
       </c>
       <c r="Q78">
-        <v>0.36385302</v>
+        <v>0.363182665</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4168336706625988</v>
+        <v>0.431461039972343</v>
       </c>
       <c r="T78">
-        <v>2.58701095460867</v>
+        <v>2.688999446849381</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.024028117073868</v>
+        <v>7.919819959709272</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1280725391936389</v>
+        <v>0.1276429974282541</v>
       </c>
       <c r="C79">
-        <v>0.9543002548031134</v>
+        <v>0.9450798317861573</v>
       </c>
       <c r="D79">
-        <v>2.268600254803113</v>
+        <v>2.277279831786157</v>
       </c>
       <c r="E79">
-        <v>1.0283</v>
+        <v>1.0462</v>
       </c>
       <c r="F79">
-        <v>1.3783</v>
+        <v>1.3962</v>
       </c>
       <c r="G79">
         <v>0.064</v>
@@ -7765,28 +7765,28 @@
         <v>0.584</v>
       </c>
       <c r="M79">
-        <v>0.07373905</v>
+        <v>0.0746967</v>
       </c>
       <c r="N79">
-        <v>0.5102609499999999</v>
+        <v>0.5093033</v>
       </c>
       <c r="O79">
-        <v>0.153078285</v>
+        <v>0.15279099</v>
       </c>
       <c r="P79">
-        <v>0.357182665</v>
+        <v>0.3565123100000001</v>
       </c>
       <c r="Q79">
-        <v>0.363182665</v>
+        <v>0.3625123100000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.431461039972343</v>
+        <v>0.4474181701284277</v>
       </c>
       <c r="T79">
-        <v>2.688999446849381</v>
+        <v>2.800259620202884</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.919819959709272</v>
+        <v>7.818283806379665</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1276429974282541</v>
+        <v>0.1272134556628693</v>
       </c>
       <c r="C80">
-        <v>0.9450798317861573</v>
+        <v>0.9359260793009099</v>
       </c>
       <c r="D80">
-        <v>2.277279831786157</v>
+        <v>2.28602607930091</v>
       </c>
       <c r="E80">
-        <v>1.0462</v>
+        <v>1.0641</v>
       </c>
       <c r="F80">
-        <v>1.3962</v>
+        <v>1.4141</v>
       </c>
       <c r="G80">
         <v>0.064</v>
@@ -7847,28 +7847,28 @@
         <v>0.584</v>
       </c>
       <c r="M80">
-        <v>0.0746967</v>
+        <v>0.07565435000000001</v>
       </c>
       <c r="N80">
-        <v>0.5093033</v>
+        <v>0.50834565</v>
       </c>
       <c r="O80">
-        <v>0.15279099</v>
+        <v>0.152503695</v>
       </c>
       <c r="P80">
-        <v>0.3565123100000001</v>
+        <v>0.355841955</v>
       </c>
       <c r="Q80">
-        <v>0.3625123100000001</v>
+        <v>0.361841955</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4474181701284277</v>
+        <v>0.4648950269660443</v>
       </c>
       <c r="T80">
-        <v>2.800259620202884</v>
+        <v>2.922116000542436</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.818283806379665</v>
+        <v>7.71931818857739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1272134556628693</v>
+        <v>0.1267839138974844</v>
       </c>
       <c r="C81">
-        <v>0.9359260793009099</v>
+        <v>0.926839768484695</v>
       </c>
       <c r="D81">
-        <v>2.28602607930091</v>
+        <v>2.294839768484695</v>
       </c>
       <c r="E81">
-        <v>1.0641</v>
+        <v>1.082</v>
       </c>
       <c r="F81">
-        <v>1.4141</v>
+        <v>1.432</v>
       </c>
       <c r="G81">
         <v>0.064</v>
@@ -7929,28 +7929,28 @@
         <v>0.584</v>
       </c>
       <c r="M81">
-        <v>0.07565435000000001</v>
+        <v>0.07661200000000001</v>
       </c>
       <c r="N81">
-        <v>0.50834565</v>
+        <v>0.507388</v>
       </c>
       <c r="O81">
-        <v>0.152503695</v>
+        <v>0.1522164</v>
       </c>
       <c r="P81">
-        <v>0.355841955</v>
+        <v>0.3551716</v>
       </c>
       <c r="Q81">
-        <v>0.361841955</v>
+        <v>0.3611716</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4648950269660443</v>
+        <v>0.4841195694874224</v>
       </c>
       <c r="T81">
-        <v>2.922116000542436</v>
+        <v>3.056158018915942</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.71931818857739</v>
+        <v>7.622826711220172</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1267839138974844</v>
+        <v>0.1268079721320997</v>
       </c>
       <c r="C82">
-        <v>0.926839768484695</v>
+        <v>0.9084443257045234</v>
       </c>
       <c r="D82">
-        <v>2.294839768484695</v>
+        <v>2.294344325704524</v>
       </c>
       <c r="E82">
-        <v>1.082</v>
+        <v>1.0999</v>
       </c>
       <c r="F82">
-        <v>1.432</v>
+        <v>1.4499</v>
       </c>
       <c r="G82">
         <v>0.064</v>
@@ -8011,45 +8011,45 @@
         <v>0.584</v>
       </c>
       <c r="M82">
-        <v>0.07661200000000001</v>
+        <v>0.07872957000000001</v>
       </c>
       <c r="N82">
-        <v>0.507388</v>
+        <v>0.5052704299999999</v>
       </c>
       <c r="O82">
-        <v>0.1522164</v>
+        <v>0.151581129</v>
       </c>
       <c r="P82">
-        <v>0.3551716</v>
+        <v>0.353689301</v>
       </c>
       <c r="Q82">
-        <v>0.3611716</v>
+        <v>0.359689301</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4841195694874224</v>
+        <v>0.5053677480636826</v>
       </c>
       <c r="T82">
-        <v>3.056158018915942</v>
+        <v>3.204309723434028</v>
       </c>
       <c r="U82">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y82">
-        <v>7.622826711220172</v>
+        <v>7.417797404456799</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1268079721320997</v>
+        <v>0.1263840303667148</v>
       </c>
       <c r="C83">
-        <v>0.9084443257045234</v>
+        <v>0.899306210756315</v>
       </c>
       <c r="D83">
-        <v>2.294344325704524</v>
+        <v>2.303106210756315</v>
       </c>
       <c r="E83">
-        <v>1.0999</v>
+        <v>1.1178</v>
       </c>
       <c r="F83">
-        <v>1.4499</v>
+        <v>1.4678</v>
       </c>
       <c r="G83">
         <v>0.064</v>
@@ -8093,28 +8093,28 @@
         <v>0.584</v>
       </c>
       <c r="M83">
-        <v>0.07872957000000001</v>
+        <v>0.07970154000000002</v>
       </c>
       <c r="N83">
-        <v>0.5052704299999999</v>
+        <v>0.50429846</v>
       </c>
       <c r="O83">
-        <v>0.151581129</v>
+        <v>0.151289538</v>
       </c>
       <c r="P83">
-        <v>0.353689301</v>
+        <v>0.353008922</v>
       </c>
       <c r="Q83">
-        <v>0.359689301</v>
+        <v>0.359008922</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5053677480636826</v>
+        <v>0.5289768353706382</v>
       </c>
       <c r="T83">
-        <v>3.204309723434028</v>
+        <v>3.368922728454124</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.417797404456799</v>
+        <v>7.32733646050001</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1263840303667148</v>
+        <v>0.12596008860133</v>
       </c>
       <c r="C84">
-        <v>0.899306210756315</v>
+        <v>0.890235273984046</v>
       </c>
       <c r="D84">
-        <v>2.303106210756315</v>
+        <v>2.311935273984046</v>
       </c>
       <c r="E84">
-        <v>1.1178</v>
+        <v>1.1357</v>
       </c>
       <c r="F84">
-        <v>1.4678</v>
+        <v>1.4857</v>
       </c>
       <c r="G84">
         <v>0.064</v>
@@ -8175,28 +8175,28 @@
         <v>0.584</v>
       </c>
       <c r="M84">
-        <v>0.07970154000000002</v>
+        <v>0.08067351000000002</v>
       </c>
       <c r="N84">
-        <v>0.50429846</v>
+        <v>0.50332649</v>
       </c>
       <c r="O84">
-        <v>0.151289538</v>
+        <v>0.150997947</v>
       </c>
       <c r="P84">
-        <v>0.353008922</v>
+        <v>0.3523285429999999</v>
       </c>
       <c r="Q84">
-        <v>0.359008922</v>
+        <v>0.3583285429999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5289768353706382</v>
+        <v>0.5553634623607651</v>
       </c>
       <c r="T84">
-        <v>3.368922728454124</v>
+        <v>3.552901969358936</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.32733646050001</v>
+        <v>7.23905529832531</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.12596008860133</v>
+        <v>0.1255361468359452</v>
       </c>
       <c r="C85">
-        <v>0.890235273984046</v>
+        <v>0.8812322909527295</v>
       </c>
       <c r="D85">
-        <v>2.311935273984046</v>
+        <v>2.32083229095273</v>
       </c>
       <c r="E85">
-        <v>1.1357</v>
+        <v>1.1536</v>
       </c>
       <c r="F85">
-        <v>1.4857</v>
+        <v>1.5036</v>
       </c>
       <c r="G85">
         <v>0.064</v>
@@ -8257,28 +8257,28 @@
         <v>0.584</v>
       </c>
       <c r="M85">
-        <v>0.08067351000000002</v>
+        <v>0.08164548000000002</v>
       </c>
       <c r="N85">
-        <v>0.50332649</v>
+        <v>0.5023545199999999</v>
       </c>
       <c r="O85">
-        <v>0.150997947</v>
+        <v>0.150706356</v>
       </c>
       <c r="P85">
-        <v>0.3523285429999999</v>
+        <v>0.351648164</v>
       </c>
       <c r="Q85">
-        <v>0.3583285429999999</v>
+        <v>0.357648164</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5553634623607651</v>
+        <v>0.5850484177246581</v>
       </c>
       <c r="T85">
-        <v>3.552901969358936</v>
+        <v>3.759878615376851</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.23905529832531</v>
+        <v>7.152876068583341</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1255361468359452</v>
+        <v>0.1251122050705605</v>
       </c>
       <c r="C86">
-        <v>0.8812322909527297</v>
+        <v>0.8722980492119241</v>
       </c>
       <c r="D86">
-        <v>2.32083229095273</v>
+        <v>2.329798049211924</v>
       </c>
       <c r="E86">
-        <v>1.1536</v>
+        <v>1.1715</v>
       </c>
       <c r="F86">
-        <v>1.5036</v>
+        <v>1.5215</v>
       </c>
       <c r="G86">
         <v>0.064</v>
@@ -8339,28 +8339,28 @@
         <v>0.584</v>
       </c>
       <c r="M86">
-        <v>0.08164548000000001</v>
+        <v>0.08261745000000001</v>
       </c>
       <c r="N86">
-        <v>0.5023545199999999</v>
+        <v>0.50138255</v>
       </c>
       <c r="O86">
-        <v>0.150706356</v>
+        <v>0.150414765</v>
       </c>
       <c r="P86">
-        <v>0.351648164</v>
+        <v>0.350967785</v>
       </c>
       <c r="Q86">
-        <v>0.357648164</v>
+        <v>0.356967785</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5850484177246577</v>
+        <v>0.6186913671370695</v>
       </c>
       <c r="T86">
-        <v>3.759878615376848</v>
+        <v>3.994452147530485</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.152876068583342</v>
+        <v>7.068724585423539</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1251122050705605</v>
+        <v>0.1246882633051756</v>
       </c>
       <c r="C87">
-        <v>0.8722980492119241</v>
+        <v>0.8634333485281189</v>
       </c>
       <c r="D87">
-        <v>2.329798049211924</v>
+        <v>2.338833348528119</v>
       </c>
       <c r="E87">
-        <v>1.1715</v>
+        <v>1.1894</v>
       </c>
       <c r="F87">
-        <v>1.5215</v>
+        <v>1.5394</v>
       </c>
       <c r="G87">
         <v>0.064</v>
@@ -8421,28 +8421,28 @@
         <v>0.584</v>
       </c>
       <c r="M87">
-        <v>0.08261745000000001</v>
+        <v>0.08358942000000001</v>
       </c>
       <c r="N87">
-        <v>0.50138255</v>
+        <v>0.5004105799999999</v>
       </c>
       <c r="O87">
-        <v>0.150414765</v>
+        <v>0.150123174</v>
       </c>
       <c r="P87">
-        <v>0.350967785</v>
+        <v>0.350287406</v>
       </c>
       <c r="Q87">
-        <v>0.356967785</v>
+        <v>0.356287406</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6186913671370695</v>
+        <v>0.6571404521798258</v>
       </c>
       <c r="T87">
-        <v>3.994452147530485</v>
+        <v>4.262536184277496</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.068724585423539</v>
+        <v>6.986530113500009</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1246882633051756</v>
+        <v>0.1242643215397908</v>
       </c>
       <c r="C88">
-        <v>0.8634333485281189</v>
+        <v>0.8546390011225498</v>
       </c>
       <c r="D88">
-        <v>2.338833348528119</v>
+        <v>2.34793900112255</v>
       </c>
       <c r="E88">
-        <v>1.1894</v>
+        <v>1.2073</v>
       </c>
       <c r="F88">
-        <v>1.5394</v>
+        <v>1.5573</v>
       </c>
       <c r="G88">
         <v>0.064</v>
@@ -8503,28 +8503,28 @@
         <v>0.584</v>
       </c>
       <c r="M88">
-        <v>0.08358942000000001</v>
+        <v>0.08456139000000001</v>
       </c>
       <c r="N88">
-        <v>0.5004105799999999</v>
+        <v>0.4994386099999999</v>
       </c>
       <c r="O88">
-        <v>0.150123174</v>
+        <v>0.149831583</v>
       </c>
       <c r="P88">
-        <v>0.350287406</v>
+        <v>0.349607027</v>
       </c>
       <c r="Q88">
-        <v>0.356287406</v>
+        <v>0.355607027</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6571404521798258</v>
+        <v>0.701504781075314</v>
       </c>
       <c r="T88">
-        <v>4.262536184277496</v>
+        <v>4.571863918985589</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.986530113500009</v>
+        <v>6.906225169666675</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1242643215397908</v>
+        <v>0.123840379774406</v>
       </c>
       <c r="C89">
-        <v>0.8546390011225498</v>
+        <v>0.8459158319146007</v>
       </c>
       <c r="D89">
-        <v>2.34793900112255</v>
+        <v>2.357115831914601</v>
       </c>
       <c r="E89">
-        <v>1.2073</v>
+        <v>1.2252</v>
       </c>
       <c r="F89">
-        <v>1.5573</v>
+        <v>1.5752</v>
       </c>
       <c r="G89">
         <v>0.064</v>
@@ -8585,28 +8585,28 @@
         <v>0.584</v>
       </c>
       <c r="M89">
-        <v>0.08456139000000001</v>
+        <v>0.08553336</v>
       </c>
       <c r="N89">
-        <v>0.4994386099999999</v>
+        <v>0.49846664</v>
       </c>
       <c r="O89">
-        <v>0.149831583</v>
+        <v>0.149539992</v>
       </c>
       <c r="P89">
-        <v>0.349607027</v>
+        <v>0.348926648</v>
       </c>
       <c r="Q89">
-        <v>0.355607027</v>
+        <v>0.354926648</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.701504781075314</v>
+        <v>0.7532631647867167</v>
       </c>
       <c r="T89">
-        <v>4.571863918985589</v>
+        <v>4.932746276145028</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.906225169666675</v>
+        <v>6.827745338193191</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.123840379774406</v>
+        <v>0.1234164380090212</v>
       </c>
       <c r="C90">
-        <v>0.8459158319146007</v>
+        <v>0.8372646787709226</v>
       </c>
       <c r="D90">
-        <v>2.357115831914601</v>
+        <v>2.366364678770922</v>
       </c>
       <c r="E90">
-        <v>1.2252</v>
+        <v>1.2431</v>
       </c>
       <c r="F90">
-        <v>1.5752</v>
+        <v>1.5931</v>
       </c>
       <c r="G90">
         <v>0.064</v>
@@ -8667,28 +8667,28 @@
         <v>0.584</v>
       </c>
       <c r="M90">
-        <v>0.08553336</v>
+        <v>0.08650533000000001</v>
       </c>
       <c r="N90">
-        <v>0.49846664</v>
+        <v>0.49749467</v>
       </c>
       <c r="O90">
-        <v>0.149539992</v>
+        <v>0.149248401</v>
       </c>
       <c r="P90">
-        <v>0.348926648</v>
+        <v>0.348246269</v>
       </c>
       <c r="Q90">
-        <v>0.354926648</v>
+        <v>0.354246269</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7532631647867167</v>
+        <v>0.8144321637183746</v>
       </c>
       <c r="T90">
-        <v>4.932746276145028</v>
+        <v>5.359243607333458</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.827745338193191</v>
+        <v>6.751029098438211</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1234164380090212</v>
+        <v>0.1229924962436364</v>
       </c>
       <c r="C91">
-        <v>0.8372646787709226</v>
+        <v>0.8286863927604464</v>
       </c>
       <c r="D91">
-        <v>2.366364678770922</v>
+        <v>2.375686392760446</v>
       </c>
       <c r="E91">
-        <v>1.2431</v>
+        <v>1.261</v>
       </c>
       <c r="F91">
-        <v>1.5931</v>
+        <v>1.611</v>
       </c>
       <c r="G91">
         <v>0.064</v>
@@ -8749,28 +8749,28 @@
         <v>0.584</v>
       </c>
       <c r="M91">
-        <v>0.08650533000000001</v>
+        <v>0.08747730000000001</v>
       </c>
       <c r="N91">
-        <v>0.49749467</v>
+        <v>0.4965227</v>
       </c>
       <c r="O91">
-        <v>0.149248401</v>
+        <v>0.14895681</v>
       </c>
       <c r="P91">
-        <v>0.348246269</v>
+        <v>0.34756589</v>
       </c>
       <c r="Q91">
-        <v>0.354246269</v>
+        <v>0.35356589</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8144321637183746</v>
+        <v>0.8878349624363641</v>
       </c>
       <c r="T91">
-        <v>5.359243607333458</v>
+        <v>5.871040404759572</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.751029098438211</v>
+        <v>6.67601766401112</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1229924962436364</v>
+        <v>0.1225685544782516</v>
       </c>
       <c r="C92">
-        <v>0.8286863927604464</v>
+        <v>0.8201818384154531</v>
       </c>
       <c r="D92">
-        <v>2.375686392760446</v>
+        <v>2.385081838415453</v>
       </c>
       <c r="E92">
-        <v>1.261</v>
+        <v>1.2789</v>
       </c>
       <c r="F92">
-        <v>1.611</v>
+        <v>1.6289</v>
       </c>
       <c r="G92">
         <v>0.064</v>
@@ -8831,28 +8831,28 @@
         <v>0.584</v>
       </c>
       <c r="M92">
-        <v>0.08747730000000001</v>
+        <v>0.08844927</v>
       </c>
       <c r="N92">
-        <v>0.4965227</v>
+        <v>0.4955507299999999</v>
       </c>
       <c r="O92">
-        <v>0.14895681</v>
+        <v>0.148665219</v>
       </c>
       <c r="P92">
-        <v>0.34756589</v>
+        <v>0.346885511</v>
       </c>
       <c r="Q92">
-        <v>0.35356589</v>
+        <v>0.352885511</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8878349624363641</v>
+        <v>0.9775494942027957</v>
       </c>
       <c r="T92">
-        <v>5.871040404759572</v>
+        <v>6.496569823835936</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.67601766401112</v>
+        <v>6.60265483253847</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1225685544782516</v>
+        <v>0.1221446127128668</v>
       </c>
       <c r="C93">
-        <v>0.8201818384154531</v>
+        <v>0.8117518939988473</v>
       </c>
       <c r="D93">
-        <v>2.385081838415453</v>
+        <v>2.394551893998847</v>
       </c>
       <c r="E93">
-        <v>1.2789</v>
+        <v>1.2968</v>
       </c>
       <c r="F93">
-        <v>1.6289</v>
+        <v>1.6468</v>
       </c>
       <c r="G93">
         <v>0.064</v>
@@ -8913,28 +8913,28 @@
         <v>0.584</v>
       </c>
       <c r="M93">
-        <v>0.08844927</v>
+        <v>0.08942124</v>
       </c>
       <c r="N93">
-        <v>0.4955507299999999</v>
+        <v>0.49457876</v>
       </c>
       <c r="O93">
-        <v>0.148665219</v>
+        <v>0.148373628</v>
       </c>
       <c r="P93">
-        <v>0.346885511</v>
+        <v>0.346205132</v>
       </c>
       <c r="Q93">
-        <v>0.352885511</v>
+        <v>0.352205132</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9775494942027957</v>
+        <v>1.089692658910836</v>
       </c>
       <c r="T93">
-        <v>6.496569823835936</v>
+        <v>7.278481597681391</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.60265483253847</v>
+        <v>6.530886845228269</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1221446127128668</v>
+        <v>0.121720670947482</v>
       </c>
       <c r="C94">
-        <v>0.8117518939988473</v>
+        <v>0.8033974517778468</v>
       </c>
       <c r="D94">
-        <v>2.394551893998847</v>
+        <v>2.404097451777847</v>
       </c>
       <c r="E94">
-        <v>1.2968</v>
+        <v>1.3147</v>
       </c>
       <c r="F94">
-        <v>1.6468</v>
+        <v>1.6647</v>
       </c>
       <c r="G94">
         <v>0.064</v>
@@ -8995,28 +8995,28 @@
         <v>0.584</v>
       </c>
       <c r="M94">
-        <v>0.08942124</v>
+        <v>0.09039321</v>
       </c>
       <c r="N94">
-        <v>0.49457876</v>
+        <v>0.49360679</v>
       </c>
       <c r="O94">
-        <v>0.148373628</v>
+        <v>0.148082037</v>
       </c>
       <c r="P94">
-        <v>0.346205132</v>
+        <v>0.345524753</v>
       </c>
       <c r="Q94">
-        <v>0.352205132</v>
+        <v>0.351524753</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.089692658910836</v>
+        <v>1.233876727821172</v>
       </c>
       <c r="T94">
-        <v>7.278481597681391</v>
+        <v>8.283796735482689</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.530886845228269</v>
+        <v>6.460662255494633</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.121720670947482</v>
+        <v>0.1212967291820972</v>
       </c>
       <c r="C95">
-        <v>0.8033974517778468</v>
+        <v>0.7951194183042178</v>
       </c>
       <c r="D95">
-        <v>2.404097451777847</v>
+        <v>2.413719418304218</v>
       </c>
       <c r="E95">
-        <v>1.3147</v>
+        <v>1.3326</v>
       </c>
       <c r="F95">
-        <v>1.6647</v>
+        <v>1.6826</v>
       </c>
       <c r="G95">
         <v>0.064</v>
@@ -9077,28 +9077,28 @@
         <v>0.584</v>
       </c>
       <c r="M95">
-        <v>0.09039321</v>
+        <v>0.09136518</v>
       </c>
       <c r="N95">
-        <v>0.49360679</v>
+        <v>0.49263482</v>
       </c>
       <c r="O95">
-        <v>0.148082037</v>
+        <v>0.147790446</v>
       </c>
       <c r="P95">
-        <v>0.345524753</v>
+        <v>0.344844374</v>
       </c>
       <c r="Q95">
-        <v>0.351524753</v>
+        <v>0.350844374</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.233876727821172</v>
+        <v>1.426122153034954</v>
       </c>
       <c r="T95">
-        <v>8.283796735482689</v>
+        <v>9.624216919217755</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.460662255494633</v>
+        <v>6.391931805968094</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1212967291820972</v>
+        <v>0.1208727874167124</v>
       </c>
       <c r="C96">
-        <v>0.7951194183042178</v>
+        <v>0.7869187147012886</v>
       </c>
       <c r="D96">
-        <v>2.413719418304218</v>
+        <v>2.423418714701289</v>
       </c>
       <c r="E96">
-        <v>1.3326</v>
+        <v>1.3505</v>
       </c>
       <c r="F96">
-        <v>1.6826</v>
+        <v>1.7005</v>
       </c>
       <c r="G96">
         <v>0.064</v>
@@ -9159,28 +9159,28 @@
         <v>0.584</v>
       </c>
       <c r="M96">
-        <v>0.09136518</v>
+        <v>0.09233715000000001</v>
       </c>
       <c r="N96">
-        <v>0.49263482</v>
+        <v>0.49166285</v>
       </c>
       <c r="O96">
-        <v>0.147790446</v>
+        <v>0.147498855</v>
       </c>
       <c r="P96">
-        <v>0.344844374</v>
+        <v>0.344163995</v>
       </c>
       <c r="Q96">
-        <v>0.350844374</v>
+        <v>0.350163995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.426122153034954</v>
+        <v>1.69526574833425</v>
       </c>
       <c r="T96">
-        <v>9.624216919217755</v>
+        <v>11.50080517644685</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.391931805968094</v>
+        <v>6.324648313273693</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1208727874167124</v>
+        <v>0.1204488456513276</v>
       </c>
       <c r="C97">
-        <v>0.7869187147012886</v>
+        <v>0.7787962769579011</v>
       </c>
       <c r="D97">
-        <v>2.423418714701289</v>
+        <v>2.433196276957901</v>
       </c>
       <c r="E97">
-        <v>1.3505</v>
+        <v>1.3684</v>
       </c>
       <c r="F97">
-        <v>1.7005</v>
+        <v>1.7184</v>
       </c>
       <c r="G97">
         <v>0.064</v>
@@ -9241,28 +9241,28 @@
         <v>0.584</v>
       </c>
       <c r="M97">
-        <v>0.09233715000000001</v>
+        <v>0.09330912000000001</v>
       </c>
       <c r="N97">
-        <v>0.49166285</v>
+        <v>0.4906908799999999</v>
       </c>
       <c r="O97">
-        <v>0.147498855</v>
+        <v>0.147207264</v>
       </c>
       <c r="P97">
-        <v>0.344163995</v>
+        <v>0.343483616</v>
       </c>
       <c r="Q97">
-        <v>0.350163995</v>
+        <v>0.349483616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.69526574833425</v>
+        <v>2.098981141283193</v>
       </c>
       <c r="T97">
-        <v>11.50080517644685</v>
+        <v>14.31568756229049</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.324648313273693</v>
+        <v>6.258766560010424</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1204488456513275</v>
+        <v>0.1200249038859427</v>
       </c>
       <c r="C98">
-        <v>0.7787962769579022</v>
+        <v>0.7707530562295086</v>
       </c>
       <c r="D98">
-        <v>2.433196276957902</v>
+        <v>2.443053056229509</v>
       </c>
       <c r="E98">
-        <v>1.3684</v>
+        <v>1.3863</v>
       </c>
       <c r="F98">
-        <v>1.7184</v>
+        <v>1.7363</v>
       </c>
       <c r="G98">
         <v>0.064</v>
@@ -9323,28 +9323,28 @@
         <v>0.584</v>
       </c>
       <c r="M98">
-        <v>0.09330912</v>
+        <v>0.09428109</v>
       </c>
       <c r="N98">
-        <v>0.4906908799999999</v>
+        <v>0.48971891</v>
       </c>
       <c r="O98">
-        <v>0.147207264</v>
+        <v>0.146915673</v>
       </c>
       <c r="P98">
-        <v>0.343483616</v>
+        <v>0.342803237</v>
       </c>
       <c r="Q98">
-        <v>0.349483616</v>
+        <v>0.348803237</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.098981141283187</v>
+        <v>2.771840129531423</v>
       </c>
       <c r="T98">
-        <v>14.31568756229045</v>
+        <v>19.00715820536317</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.258766560010425</v>
+        <v>6.19424319341238</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1200249038859427</v>
+        <v>0.1196009621205579</v>
       </c>
       <c r="C99">
-        <v>0.7707530562295086</v>
+        <v>0.7627900191466193</v>
       </c>
       <c r="D99">
-        <v>2.443053056229509</v>
+        <v>2.452990019146619</v>
       </c>
       <c r="E99">
-        <v>1.3863</v>
+        <v>1.4042</v>
       </c>
       <c r="F99">
-        <v>1.7363</v>
+        <v>1.7542</v>
       </c>
       <c r="G99">
         <v>0.064</v>
@@ -9405,28 +9405,28 @@
         <v>0.584</v>
       </c>
       <c r="M99">
-        <v>0.09428109</v>
+        <v>0.09525306</v>
       </c>
       <c r="N99">
-        <v>0.48971891</v>
+        <v>0.48874694</v>
       </c>
       <c r="O99">
-        <v>0.146915673</v>
+        <v>0.146624082</v>
       </c>
       <c r="P99">
-        <v>0.342803237</v>
+        <v>0.342122858</v>
       </c>
       <c r="Q99">
-        <v>0.348803237</v>
+        <v>0.348122858</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.771840129531423</v>
+        <v>4.117558106027894</v>
       </c>
       <c r="T99">
-        <v>19.00715820536317</v>
+        <v>28.39009949150859</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.19424319341238</v>
+        <v>6.131036630214294</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1196009621205579</v>
+        <v>0.1198700203551732</v>
       </c>
       <c r="C100">
-        <v>0.7627900191466193</v>
+        <v>0.7385740939421277</v>
       </c>
       <c r="D100">
-        <v>2.452990019146619</v>
+        <v>2.446674093942128</v>
       </c>
       <c r="E100">
-        <v>1.4042</v>
+        <v>1.4221</v>
       </c>
       <c r="F100">
-        <v>1.7542</v>
+        <v>1.7721</v>
       </c>
       <c r="G100">
         <v>0.064</v>
@@ -9487,129 +9487,47 @@
         <v>0.584</v>
       </c>
       <c r="M100">
-        <v>0.09525306</v>
+        <v>0.09799713</v>
       </c>
       <c r="N100">
-        <v>0.48874694</v>
+        <v>0.48600287</v>
       </c>
       <c r="O100">
-        <v>0.146624082</v>
+        <v>0.145800861</v>
       </c>
       <c r="P100">
-        <v>0.342122858</v>
+        <v>0.340202009</v>
       </c>
       <c r="Q100">
-        <v>0.348122858</v>
+        <v>0.346202009</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.117558106027894</v>
+        <v>8.154712035517308</v>
       </c>
       <c r="T100">
-        <v>28.39009949150859</v>
+        <v>56.53892334994487</v>
       </c>
       <c r="U100">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V100">
         <v>0.3</v>
       </c>
       <c r="W100">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>6.131036630214294</v>
+        <v>5.959358197530887</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1198700203551732</v>
-      </c>
-      <c r="C101">
-        <v>0.7385740939421277</v>
-      </c>
-      <c r="D101">
-        <v>2.446674093942128</v>
-      </c>
-      <c r="E101">
-        <v>1.4221</v>
-      </c>
-      <c r="F101">
-        <v>1.7721</v>
-      </c>
-      <c r="G101">
-        <v>0.064</v>
-      </c>
-      <c r="H101">
-        <v>1.44</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.59</v>
-      </c>
-      <c r="K101">
-        <v>0.006</v>
-      </c>
-      <c r="L101">
-        <v>0.584</v>
-      </c>
-      <c r="M101">
-        <v>0.09799713</v>
-      </c>
-      <c r="N101">
-        <v>0.48600287</v>
-      </c>
-      <c r="O101">
-        <v>0.145800861</v>
-      </c>
-      <c r="P101">
-        <v>0.340202009</v>
-      </c>
-      <c r="Q101">
-        <v>0.346202009</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.154712035517308</v>
-      </c>
-      <c r="T101">
-        <v>56.53892334994487</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.959358197530887</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
